--- a/analysis/data_1.xlsx
+++ b/analysis/data_1.xlsx
@@ -8,40 +8,39 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ACER\Desktop\data-analitika\6-oy-Statistics\Exam\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59903A9E-1E24-4267-9214-283D89FEF8F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDAFF9ED-9967-40B4-827C-9B9DC8DBA946}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="data" sheetId="1" r:id="rId1"/>
-    <sheet name="Simple Regression" sheetId="5" r:id="rId2"/>
-    <sheet name="Multiple Regression" sheetId="6" r:id="rId3"/>
-    <sheet name="Hypothesis Testing" sheetId="8" r:id="rId4"/>
-    <sheet name="Ab-Testing" sheetId="13" r:id="rId5"/>
-    <sheet name="Anova" sheetId="9" r:id="rId6"/>
-    <sheet name="Charts" sheetId="3" r:id="rId7"/>
-    <sheet name="Monthly_Sales" sheetId="2" r:id="rId8"/>
+    <sheet name="Regression Diagnostics" sheetId="15" r:id="rId1"/>
+    <sheet name="data" sheetId="1" r:id="rId2"/>
+    <sheet name="Simple Regression" sheetId="5" r:id="rId3"/>
+    <sheet name="Multiple Regression" sheetId="6" r:id="rId4"/>
+    <sheet name="Hypothesis Testing" sheetId="8" r:id="rId5"/>
+    <sheet name="Ab-Testing" sheetId="13" r:id="rId6"/>
+    <sheet name="Anova" sheetId="9" r:id="rId7"/>
+    <sheet name="Charts" sheetId="3" r:id="rId8"/>
+    <sheet name="Monthly_Sales" sheetId="2" r:id="rId9"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId9"/>
+    <externalReference r:id="rId10"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlchart.v1.0" hidden="1">[1]Employee_Data!$G$1</definedName>
-    <definedName name="_xlchart.v1.1" hidden="1">[1]Employee_Data!$G$2:$G$151</definedName>
-    <definedName name="_xlchart.v1.2" hidden="1">data!$H$1</definedName>
-    <definedName name="_xlchart.v1.3" hidden="1">data!$H$2:$H$151</definedName>
+    <definedName name="_xlchart.v1.0" hidden="1">data!$G$1</definedName>
+    <definedName name="_xlchart.v1.1" hidden="1">data!$G$2:$G$151</definedName>
+    <definedName name="_xlchart.v1.2" hidden="1">[1]Employee_Data!$G$1</definedName>
+    <definedName name="_xlchart.v1.3" hidden="1">[1]Employee_Data!$G$2:$G$151</definedName>
     <definedName name="_xlchart.v1.4" hidden="1">[1]Employee_Data!$H$1</definedName>
     <definedName name="_xlchart.v1.5" hidden="1">[1]Employee_Data!$H$2:$H$151</definedName>
-    <definedName name="_xlchart.v1.6" hidden="1">[1]Employee_Data!$G$1</definedName>
-    <definedName name="_xlchart.v1.7" hidden="1">[1]Employee_Data!$G$2:$G$151</definedName>
-    <definedName name="_xlchart.v1.8" hidden="1">data!$G$1</definedName>
-    <definedName name="_xlchart.v1.9" hidden="1">data!$G$2:$G$151</definedName>
+    <definedName name="_xlchart.v1.6" hidden="1">data!$H$1</definedName>
+    <definedName name="_xlchart.v1.7" hidden="1">data!$H$2:$H$151</definedName>
     <definedName name="_xlcn.WorksheetConnection_dataK1L1511" hidden="1">data!$K$1:$L$151</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="38" r:id="rId10"/>
-    <pivotCache cacheId="60" r:id="rId11"/>
+    <pivotCache cacheId="4" r:id="rId11"/>
+    <pivotCache cacheId="8" r:id="rId12"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{FCE2AD5D-F65C-4FA6-A056-5C36A1767C68}">
@@ -90,7 +89,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -112,7 +111,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="674" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="760" uniqueCount="145">
   <si>
     <t>Employee_ID</t>
   </si>
@@ -542,11 +541,20 @@
   <si>
     <t>Chi-Square Test</t>
   </si>
+  <si>
+    <t>VIF</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="165" formatCode="m/d;@"/>
+  </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -587,12 +595,18 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="3">
@@ -627,12 +641,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -642,14 +667,12 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4081,7 +4104,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Exam data.xlsx]Charts!PivotTable26</c:name>
+    <c:name>[data_1.xlsx]Charts!PivotTable26</c:name>
     <c:fmtId val="3"/>
   </c:pivotSource>
   <c:chart>
@@ -4556,12 +4579,797 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Monthly</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> Sales </a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Monthly_Sales!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Monthly_Sales</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="12700" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDash"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:cat>
+            <c:strRef>
+              <c:f>Monthly_Sales!$A$2:$A$61</c:f>
+              <c:strCache>
+                <c:ptCount val="60"/>
+                <c:pt idx="0">
+                  <c:v>2022-01</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2022-02</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2022-03</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2022-04</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2022-05</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2022-06</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2022-07</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2022-08</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2022-09</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2022-10</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2022-11</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2022-12</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2023-01</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2023-02</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2023-03</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2023-04</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2023-05</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2023-06</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2023-07</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2023-08</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2023-09</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2023-10</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2023-11</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2023-12</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2024-01</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2024-02</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>2024-03</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>2024-04</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>2024-05</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>2024-06</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>2024-07</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>2024-08</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>2024-09</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>2024-10</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>2024-11</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>2024-12</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>2025-01</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>2025-02</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>2025-03</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>2025-04</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>2025-05</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>2025-06</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>2025-07</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>2025-08</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>2025-09</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>2025-10</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>2025-11</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>2025-12</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>2026-01</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>2026-02</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>2026-03</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>2026-04</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>2026-05</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>2026-06</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>2026-07</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>2026-08</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>2026-09</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>2026-10</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>2026-11</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>2026-12</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Monthly_Sales!$B$2:$B$61</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="60"/>
+                <c:pt idx="0">
+                  <c:v>87808</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>96364</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>90582</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>95832</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>98707</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>98061</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>100255</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>105651</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>99405</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>102381</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>106716</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>111524</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>104985</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>106627</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>106374</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>105689</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>107937</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>113121</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>117240</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>117545</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>114472</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>114462</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>121678</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>124990</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>115698</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>118914</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>119004</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>123954</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>126494</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>131204</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>132859</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>133709</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>130755</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>129440</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>135696</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>136566</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>136640</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>133780</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>134630</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>135397</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>138166</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>144659</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>144896</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>148857</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>144603</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>144497</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>146070</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>154181</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>144519</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>151971</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>150102</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>150294</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>153369</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>157632</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>158664</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>157602</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>158864</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>160030</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>163789</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>171561</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-CB49-4557-8D2D-6C540FF3FAA7}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="506086560"/>
+        <c:axId val="506085120"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="506086560"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Month</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="506085120"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="506085120"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Sales</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="506086560"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/chartEx1.xml><?xml version="1.0" encoding="utf-8"?>
 <cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
   <cx:chartData>
     <cx:data id="0">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.3</cx:f>
+        <cx:f>_xlchart.v1.7</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -4599,7 +5407,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{00000000-1A4F-4DEF-AF5E-7E77F000A4A4}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.2</cx:f>
+              <cx:f>_xlchart.v1.6</cx:f>
               <cx:v>Performance_Score</cx:v>
             </cx:txData>
           </cx:tx>
@@ -4629,7 +5437,7 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.7</cx:f>
+        <cx:f>_xlchart.v1.3</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -4667,7 +5475,7 @@
         <cx:series layoutId="clusteredColumn" uniqueId="{00000000-3913-4FB0-A18B-9A188AEC480B}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.6</cx:f>
+              <cx:f>_xlchart.v1.2</cx:f>
               <cx:v>Salary</cx:v>
             </cx:txData>
           </cx:tx>
@@ -4701,7 +5509,7 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.9</cx:f>
+        <cx:f>_xlchart.v1.1</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -4739,7 +5547,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{00000000-D60C-4F63-8D6C-528E01ABC2CC}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.8</cx:f>
+              <cx:f>_xlchart.v1.0</cx:f>
               <cx:v>Salary</cx:v>
             </cx:txData>
           </cx:tx>
@@ -5034,6 +5842,46 @@
 </file>
 
 <file path=xl/charts/colors6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors7.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -8138,6 +8986,522 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
@@ -8187,8 +9551,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="5572125" y="0"/>
-              <a:ext cx="4555331" cy="2607469"/>
+              <a:off x="5319712" y="0"/>
+              <a:ext cx="5310188" cy="2667476"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -8265,8 +9629,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="0" y="5494020"/>
-              <a:ext cx="4572000" cy="2743200"/>
+              <a:off x="0" y="5676900"/>
+              <a:ext cx="4305300" cy="2743200"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -8344,7 +9708,7 @@
           <xdr:spPr>
             <a:xfrm>
               <a:off x="1" y="0"/>
-              <a:ext cx="4810124" cy="2583655"/>
+              <a:ext cx="4557711" cy="2643662"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -8421,8 +9785,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="5494879" y="5594195"/>
-              <a:ext cx="4688160" cy="2862146"/>
+              <a:off x="5224462" y="5686193"/>
+              <a:ext cx="5410201" cy="2817541"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -8566,6 +9930,44 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>101</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>369570</xdr:colOff>
+      <xdr:row>118</xdr:row>
+      <xdr:rowOff>157289</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E983C7D3-ED1A-497E-9418-7BD0A10F10B5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId8"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -9804,7 +11206,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="ACER" refreshedDate="46178.900923842593" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{9FBFA905-FD10-4D82-A392-1B12B7F6F24D}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="ACER" refreshedDate="46179.528487152777" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{9FBFA905-FD10-4D82-A392-1B12B7F6F24D}">
   <cacheSource type="external" connectionId="1"/>
   <cacheFields count="3">
     <cacheField name="[Range].[Website_Group].[Website_Group]" caption="Website_Group" numFmtId="0" level="1">
@@ -9882,7 +11284,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="ACER" refreshedDate="46178.924039120371" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="150" xr:uid="{6F265953-A80A-448F-B008-FC467DD77582}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="ACER" refreshedDate="46179.528487384261" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="150" xr:uid="{6F265953-A80A-448F-B008-FC467DD77582}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:L151" sheet="data"/>
   </cacheSource>
@@ -12041,7 +13443,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{DFE2E4DF-3236-460A-B99F-EA36CE779646}" name="PivotTable13" cacheId="38" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{DFE2E4DF-3236-460A-B99F-EA36CE779646}" name="PivotTable13" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:D7" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="3">
     <pivotField axis="axisRow" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
@@ -12121,7 +13523,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BBA63960-8FC4-4E13-A0FE-E2F5E0603A8F}" name="PivotTable26" cacheId="60" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="4">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BBA63960-8FC4-4E13-A0FE-E2F5E0603A8F}" name="PivotTable26" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="4">
   <location ref="F82:G84" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="12">
     <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0">
@@ -12537,6 +13939,700 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AA77A4B-ED43-4AB8-981B-967AB92F23B8}">
+  <dimension ref="A1:I65"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="18.109375" customWidth="1"/>
+    <col min="2" max="2" width="19.88671875" customWidth="1"/>
+    <col min="3" max="3" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="9" width="9" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="B3" s="12"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="B4" s="9">
+        <v>0.91720765647857849</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="B5" s="13">
+        <v>0.84126988510292611</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="B6" s="9">
+        <v>0.84019738432659452</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="B7" s="9">
+        <v>639.21684285859385</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="B8" s="10">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A11" s="11"/>
+      <c r="B11" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A12" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B12" s="9">
+        <v>1</v>
+      </c>
+      <c r="C12" s="9">
+        <v>320504511.47527212</v>
+      </c>
+      <c r="D12" s="9">
+        <v>320504511.47527212</v>
+      </c>
+      <c r="E12" s="9">
+        <v>784.4002574808718</v>
+      </c>
+      <c r="F12" s="9">
+        <v>5.0333113587551144E-61</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A13" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="B13" s="9">
+        <v>148</v>
+      </c>
+      <c r="C13" s="9">
+        <v>60472529.484728023</v>
+      </c>
+      <c r="D13" s="9">
+        <v>408598.17219410825</v>
+      </c>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
+    </row>
+    <row r="14" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="B14" s="10">
+        <v>149</v>
+      </c>
+      <c r="C14" s="10">
+        <v>380977040.96000016</v>
+      </c>
+      <c r="D14" s="10"/>
+      <c r="E14" s="10"/>
+      <c r="F14" s="10"/>
+    </row>
+    <row r="15" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A16" s="11"/>
+      <c r="B16" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="F16" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="G16" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="H16" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="I16" s="11" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A17" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="B17" s="9">
+        <v>3110.4921631488724</v>
+      </c>
+      <c r="C17" s="9">
+        <v>82.292753402388882</v>
+      </c>
+      <c r="D17" s="9">
+        <v>37.797886624833453</v>
+      </c>
+      <c r="E17" s="9">
+        <v>6.360910963088989E-78</v>
+      </c>
+      <c r="F17" s="9">
+        <v>2947.8716020890029</v>
+      </c>
+      <c r="G17" s="9">
+        <v>3273.1127242087418</v>
+      </c>
+      <c r="H17" s="9">
+        <v>2947.8716020890029</v>
+      </c>
+      <c r="I17" s="9">
+        <v>3273.1127242087418</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="B18" s="10">
+        <v>158.63037123303806</v>
+      </c>
+      <c r="C18" s="10">
+        <v>5.6639247768247305</v>
+      </c>
+      <c r="D18" s="10">
+        <v>28.007146542996338</v>
+      </c>
+      <c r="E18" s="10">
+        <v>5.0333113587551144E-61</v>
+      </c>
+      <c r="F18" s="10">
+        <v>147.43776207941852</v>
+      </c>
+      <c r="G18" s="10">
+        <v>169.8229803866576</v>
+      </c>
+      <c r="H18" s="10">
+        <v>147.43776207941852</v>
+      </c>
+      <c r="I18" s="10">
+        <v>169.8229803866576</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A24" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="B24" s="12"/>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A25" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="B25" s="9">
+        <v>0.62623626351475936</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A26" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="B26" s="13">
+        <v>0.39217185774092711</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A27" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="B27" s="9">
+        <v>0.3880649108337712</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A28" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="B28" s="9">
+        <v>1250.8606957083905</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="B29" s="10">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A32" s="11"/>
+      <c r="B32" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="C32" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="D32" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="E32" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="F32" s="11" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A33" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B33" s="9">
+        <v>1</v>
+      </c>
+      <c r="C33" s="9">
+        <v>149408473.90992454</v>
+      </c>
+      <c r="D33" s="9">
+        <v>149408473.90992454</v>
+      </c>
+      <c r="E33" s="9">
+        <v>95.489877664990331</v>
+      </c>
+      <c r="F33" s="9">
+        <v>1.0345184962298565E-17</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A34" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="B34" s="9">
+        <v>148</v>
+      </c>
+      <c r="C34" s="9">
+        <v>231568567.05007562</v>
+      </c>
+      <c r="D34" s="9">
+        <v>1564652.4800680785</v>
+      </c>
+      <c r="E34" s="9"/>
+      <c r="F34" s="9"/>
+    </row>
+    <row r="35" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="B35" s="10">
+        <v>149</v>
+      </c>
+      <c r="C35" s="10">
+        <v>380977040.96000016</v>
+      </c>
+      <c r="D35" s="10"/>
+      <c r="E35" s="10"/>
+      <c r="F35" s="10"/>
+    </row>
+    <row r="36" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A37" s="11"/>
+      <c r="B37" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="C37" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="D37" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="E37" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="F37" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="G37" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="H37" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="I37" s="11" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A38" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="B38" s="9">
+        <v>745.66434315816787</v>
+      </c>
+      <c r="C38" s="9">
+        <v>436.47485129266187</v>
+      </c>
+      <c r="D38" s="9">
+        <v>1.7083787094486931</v>
+      </c>
+      <c r="E38" s="9">
+        <v>8.9662516984095164E-2</v>
+      </c>
+      <c r="F38" s="9">
+        <v>-116.86342837797497</v>
+      </c>
+      <c r="G38" s="9">
+        <v>1608.1921146943107</v>
+      </c>
+      <c r="H38" s="9">
+        <v>-116.86342837797497</v>
+      </c>
+      <c r="I38" s="9">
+        <v>1608.1921146943107</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="B39" s="10">
+        <v>96.706521847990473</v>
+      </c>
+      <c r="C39" s="10">
+        <v>9.8963966872805216</v>
+      </c>
+      <c r="D39" s="10">
+        <v>9.7718922254080471</v>
+      </c>
+      <c r="E39" s="10">
+        <v>1.034518496229901E-17</v>
+      </c>
+      <c r="F39" s="10">
+        <v>77.150029748530898</v>
+      </c>
+      <c r="G39" s="10">
+        <v>116.26301394745005</v>
+      </c>
+      <c r="H39" s="10">
+        <v>77.150029748530898</v>
+      </c>
+      <c r="I39" s="10">
+        <v>116.26301394745005</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A44" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="B44" s="12"/>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A45" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="B45" s="9">
+        <v>0.25911804999819932</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A46" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="B46" s="13">
+        <v>6.7142163834869317E-2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A47" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="B47" s="9">
+        <v>6.0839070347267078E-2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A48" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="B48" s="9">
+        <v>1549.6237949260287</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="B49" s="10">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A52" s="11"/>
+      <c r="B52" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="C52" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="D52" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="E52" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="F52" s="11" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A53" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B53" s="9">
+        <v>1</v>
+      </c>
+      <c r="C53" s="9">
+        <v>25579622.901460052</v>
+      </c>
+      <c r="D53" s="9">
+        <v>25579622.901460052</v>
+      </c>
+      <c r="E53" s="9">
+        <v>10.652255748218474</v>
+      </c>
+      <c r="F53" s="9">
+        <v>1.365458636838886E-3</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A54" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="B54" s="9">
+        <v>148</v>
+      </c>
+      <c r="C54" s="9">
+        <v>355397418.05854011</v>
+      </c>
+      <c r="D54" s="9">
+        <v>2401333.9058009465</v>
+      </c>
+      <c r="E54" s="9"/>
+      <c r="F54" s="9"/>
+    </row>
+    <row r="55" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A55" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="B55" s="10">
+        <v>149</v>
+      </c>
+      <c r="C55" s="10">
+        <v>380977040.96000016</v>
+      </c>
+      <c r="D55" s="10"/>
+      <c r="E55" s="10"/>
+      <c r="F55" s="10"/>
+    </row>
+    <row r="56" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A57" s="11"/>
+      <c r="B57" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="C57" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="D57" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="E57" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="F57" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="G57" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="H57" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="I57" s="11" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A58" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="B58" s="9">
+        <v>4010.4144525547431</v>
+      </c>
+      <c r="C58" s="9">
+        <v>298.39933368975159</v>
+      </c>
+      <c r="D58" s="9">
+        <v>13.439756727890037</v>
+      </c>
+      <c r="E58" s="9">
+        <v>2.02775595189212E-27</v>
+      </c>
+      <c r="F58" s="9">
+        <v>3420.7408171710717</v>
+      </c>
+      <c r="G58" s="9">
+        <v>4600.0880879384149</v>
+      </c>
+      <c r="H58" s="9">
+        <v>3420.7408171710717</v>
+      </c>
+      <c r="I58" s="9">
+        <v>4600.0880879384149</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A59" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B59" s="10">
+        <v>529.21532846715388</v>
+      </c>
+      <c r="C59" s="10">
+        <v>162.14800976519356</v>
+      </c>
+      <c r="D59" s="10">
+        <v>3.2637793657381935</v>
+      </c>
+      <c r="E59" s="10">
+        <v>1.36545863683894E-3</v>
+      </c>
+      <c r="F59" s="10">
+        <v>208.79099907545395</v>
+      </c>
+      <c r="G59" s="10">
+        <v>849.63965785885375</v>
+      </c>
+      <c r="H59" s="10">
+        <v>208.79099907545395</v>
+      </c>
+      <c r="I59" s="10">
+        <v>849.63965785885375</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B62" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>1</v>
+      </c>
+      <c r="B63">
+        <f>1/(1-B26)</f>
+        <v>1.6452018761147995</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>2</v>
+      </c>
+      <c r="B64">
+        <f>1/(1-B5)</f>
+        <v>6.3000017397356176</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>3</v>
+      </c>
+      <c r="B65">
+        <f>1/(1-B46)</f>
+        <v>1.0719747010014762</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O151"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -12706,7 +14802,7 @@
       <c r="L4">
         <v>0</v>
       </c>
-      <c r="O4" s="8"/>
+      <c r="O4" s="6"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5">
@@ -18300,7 +20396,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFAE4228-6AB5-4FCA-912B-AD14BFE79650}">
   <dimension ref="A1:I174"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -18320,48 +20416,48 @@
     </row>
     <row r="2" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="B3" s="7"/>
+      <c r="B3" s="3"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
+      <c r="A4" t="s">
         <v>90</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4">
         <v>0.91720765647857849</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
+      <c r="A5" t="s">
         <v>91</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5">
         <v>0.84126988510292611</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6" s="4" t="s">
+      <c r="A6" t="s">
         <v>92</v>
       </c>
-      <c r="B6" s="4">
+      <c r="B6">
         <v>0.84019738432659452</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7" s="4" t="s">
+      <c r="A7" t="s">
         <v>93</v>
       </c>
-      <c r="B7" s="4">
+      <c r="B7">
         <v>639.21684285859385</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="B8" s="5">
+      <c r="B8" s="4">
         <v>150</v>
       </c>
     </row>
@@ -18371,156 +20467,154 @@
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A11" s="6"/>
-      <c r="B11" s="6" t="s">
+      <c r="A11" s="5"/>
+      <c r="B11" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="E11" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="F11" s="6" t="s">
+      <c r="F11" s="5" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A12" s="4" t="s">
+      <c r="A12" t="s">
         <v>96</v>
       </c>
-      <c r="B12" s="4">
+      <c r="B12">
         <v>1</v>
       </c>
-      <c r="C12" s="4">
+      <c r="C12">
         <v>320504511.47527212</v>
       </c>
-      <c r="D12" s="4">
+      <c r="D12">
         <v>320504511.47527212</v>
       </c>
-      <c r="E12" s="4">
+      <c r="E12">
         <v>784.4002574808718</v>
       </c>
-      <c r="F12" s="4">
+      <c r="F12">
         <v>5.0333113587551144E-61</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A13" s="4" t="s">
+      <c r="A13" t="s">
         <v>97</v>
       </c>
-      <c r="B13" s="4">
+      <c r="B13">
         <v>148</v>
       </c>
-      <c r="C13" s="4">
+      <c r="C13">
         <v>60472529.484728023</v>
       </c>
-      <c r="D13" s="4">
+      <c r="D13">
         <v>408598.17219410825</v>
       </c>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
     </row>
     <row r="14" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="B14" s="5">
+      <c r="B14" s="4">
         <v>149</v>
       </c>
-      <c r="C14" s="5">
+      <c r="C14" s="4">
         <v>380977040.96000016</v>
       </c>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
     </row>
     <row r="15" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A16" s="6"/>
-      <c r="B16" s="6" t="s">
+      <c r="A16" s="5"/>
+      <c r="B16" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="D16" s="6" t="s">
+      <c r="D16" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="E16" s="6" t="s">
+      <c r="E16" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="F16" s="6" t="s">
+      <c r="F16" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="G16" s="6" t="s">
+      <c r="G16" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="H16" s="6" t="s">
+      <c r="H16" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="I16" s="6" t="s">
+      <c r="I16" s="5" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A17" s="4" t="s">
+      <c r="A17" t="s">
         <v>99</v>
       </c>
-      <c r="B17" s="4">
+      <c r="B17">
         <v>3110.4921631488724</v>
       </c>
-      <c r="C17" s="4">
+      <c r="C17">
         <v>82.292753402388882</v>
       </c>
-      <c r="D17" s="4">
+      <c r="D17">
         <v>37.797886624833453</v>
       </c>
-      <c r="E17" s="4">
+      <c r="E17">
         <v>6.360910963088989E-78</v>
       </c>
-      <c r="F17" s="4">
+      <c r="F17">
         <v>2947.8716020890029</v>
       </c>
-      <c r="G17" s="4">
+      <c r="G17">
         <v>3273.1127242087418</v>
       </c>
-      <c r="H17" s="4">
+      <c r="H17">
         <v>2947.8716020890029</v>
       </c>
-      <c r="I17" s="4">
+      <c r="I17">
         <v>3273.1127242087418</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B18" s="5">
+      <c r="B18" s="4">
         <v>158.63037123303806</v>
       </c>
-      <c r="C18" s="5">
+      <c r="C18" s="4">
         <v>5.6639247768247305</v>
       </c>
-      <c r="D18" s="5">
+      <c r="D18" s="4">
         <v>28.007146542996338</v>
       </c>
-      <c r="E18" s="5">
+      <c r="E18" s="4">
         <v>5.0333113587551144E-61</v>
       </c>
-      <c r="F18" s="5">
+      <c r="F18" s="4">
         <v>147.43776207941852</v>
       </c>
-      <c r="G18" s="5">
+      <c r="G18" s="4">
         <v>169.8229803866576</v>
       </c>
-      <c r="H18" s="5">
+      <c r="H18" s="4">
         <v>147.43776207941852</v>
       </c>
-      <c r="I18" s="5">
+      <c r="I18" s="4">
         <v>169.8229803866576</v>
       </c>
     </row>
@@ -18531,1663 +20625,1663 @@
     </row>
     <row r="23" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A24" s="6" t="s">
+      <c r="A24" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="B24" s="6" t="s">
+      <c r="B24" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="C24" s="6" t="s">
+      <c r="C24" s="5" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A25" s="4">
+      <c r="A25">
         <v>1</v>
       </c>
-      <c r="B25" s="4">
+      <c r="B25">
         <v>3110.4921631488724</v>
       </c>
-      <c r="C25" s="4">
+      <c r="C25">
         <v>670.50783685112765</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A26" s="4">
+      <c r="A26">
         <v>2</v>
       </c>
-      <c r="B26" s="4">
+      <c r="B26">
         <v>3586.3832768479865</v>
       </c>
-      <c r="C26" s="4">
+      <c r="C26">
         <v>428.61672315201349</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A27" s="4">
+      <c r="A27">
         <v>3</v>
       </c>
-      <c r="B27" s="4">
+      <c r="B27">
         <v>3110.4921631488724</v>
       </c>
-      <c r="C27" s="4">
+      <c r="C27">
         <v>139.50783685112765</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A28" s="4">
+      <c r="A28">
         <v>4</v>
       </c>
-      <c r="B28" s="4">
+      <c r="B28">
         <v>6124.4692165765955</v>
       </c>
-      <c r="C28" s="4">
+      <c r="C28">
         <v>192.5307834234045</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A29" s="4">
+      <c r="A29">
         <v>5</v>
       </c>
-      <c r="B29" s="4">
+      <c r="B29">
         <v>5965.8388453435573</v>
       </c>
-      <c r="C29" s="4">
+      <c r="C29">
         <v>-1099.8388453435573</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A30" s="4">
+      <c r="A30">
         <v>6</v>
       </c>
-      <c r="B30" s="4">
+      <c r="B30">
         <v>3903.6440193140625</v>
       </c>
-      <c r="C30" s="4">
+      <c r="C30">
         <v>-422.64401931406246</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A31" s="4">
+      <c r="A31">
         <v>7</v>
       </c>
-      <c r="B31" s="4">
+      <c r="B31">
         <v>4379.5351330131771</v>
       </c>
-      <c r="C31" s="4">
+      <c r="C31">
         <v>1162.4648669868229</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A32" s="4">
+      <c r="A32">
         <v>8</v>
       </c>
-      <c r="B32" s="4">
+      <c r="B32">
         <v>6283.0995878096337</v>
       </c>
-      <c r="C32" s="4">
+      <c r="C32">
         <v>-270.0995878096337</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A33" s="4">
+      <c r="A33">
         <v>9</v>
       </c>
-      <c r="B33" s="4">
+      <c r="B33">
         <v>5965.8388453435573</v>
       </c>
-      <c r="C33" s="4">
+      <c r="C33">
         <v>-244.8388453435573</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A34" s="4">
+      <c r="A34">
         <v>10</v>
       </c>
-      <c r="B34" s="4">
+      <c r="B34">
         <v>6124.4692165765955</v>
       </c>
-      <c r="C34" s="4">
+      <c r="C34">
         <v>-217.4692165765955</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A35" s="4">
+      <c r="A35">
         <v>11</v>
       </c>
-      <c r="B35" s="4">
+      <c r="B35">
         <v>3586.3832768479865</v>
       </c>
-      <c r="C35" s="4">
+      <c r="C35">
         <v>-481.38327684798651</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A36" s="4">
+      <c r="A36">
         <v>12</v>
       </c>
-      <c r="B36" s="4">
+      <c r="B36">
         <v>5014.056617945329</v>
       </c>
-      <c r="C36" s="4">
+      <c r="C36">
         <v>-523.05661794532898</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A37" s="4">
+      <c r="A37">
         <v>13</v>
       </c>
-      <c r="B37" s="4">
+      <c r="B37">
         <v>4220.9047617801389</v>
       </c>
-      <c r="C37" s="4">
+      <c r="C37">
         <v>36.09523821986113</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A38" s="4">
+      <c r="A38">
         <v>14</v>
       </c>
-      <c r="B38" s="4">
+      <c r="B38">
         <v>7869.4033001400139</v>
       </c>
-      <c r="C38" s="4">
+      <c r="C38">
         <v>278.59669985998607</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A39" s="4">
+      <c r="A39">
         <v>15</v>
       </c>
-      <c r="B39" s="4">
+      <c r="B39">
         <v>7552.1425576739384</v>
       </c>
-      <c r="C39" s="4">
+      <c r="C39">
         <v>-817.14255767393843</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A40" s="4">
+      <c r="A40">
         <v>16</v>
       </c>
-      <c r="B40" s="4">
+      <c r="B40">
         <v>3269.1225343819106</v>
       </c>
-      <c r="C40" s="4">
+      <c r="C40">
         <v>-951.12253438191055</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A41" s="4">
+      <c r="A41">
         <v>17</v>
       </c>
-      <c r="B41" s="4">
+      <c r="B41">
         <v>7076.2514439748238</v>
       </c>
-      <c r="C41" s="4">
+      <c r="C41">
         <v>-154.25144397482381</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A42" s="4">
+      <c r="A42">
         <v>18</v>
       </c>
-      <c r="B42" s="4">
+      <c r="B42">
         <v>3110.4921631488724</v>
       </c>
-      <c r="C42" s="4">
+      <c r="C42">
         <v>-542.49216314887235</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A43" s="4">
+      <c r="A43">
         <v>19</v>
       </c>
-      <c r="B43" s="4">
+      <c r="B43">
         <v>5331.3173604114054</v>
       </c>
-      <c r="C43" s="4">
+      <c r="C43">
         <v>-621.31736041140539</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A44" s="4">
+      <c r="A44">
         <v>20</v>
       </c>
-      <c r="B44" s="4">
+      <c r="B44">
         <v>7869.4033001400139</v>
       </c>
-      <c r="C44" s="4">
+      <c r="C44">
         <v>-768.40330014001393</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A45" s="4">
+      <c r="A45">
         <v>21</v>
       </c>
-      <c r="B45" s="4">
+      <c r="B45">
         <v>8028.0336713730521</v>
       </c>
-      <c r="C45" s="4">
+      <c r="C45">
         <v>-1336.0336713730521</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A46" s="4">
+      <c r="A46">
         <v>22</v>
       </c>
-      <c r="B46" s="4">
+      <c r="B46">
         <v>4696.7958754792526</v>
       </c>
-      <c r="C46" s="4">
+      <c r="C46">
         <v>-388.79587547925257</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A47" s="4">
+      <c r="A47">
         <v>23</v>
       </c>
-      <c r="B47" s="4">
+      <c r="B47">
         <v>3427.7529056149483</v>
       </c>
-      <c r="C47" s="4">
+      <c r="C47">
         <v>-308.7529056149483</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A48" s="4">
+      <c r="A48">
         <v>24</v>
       </c>
-      <c r="B48" s="4">
+      <c r="B48">
         <v>5331.3173604114054</v>
       </c>
-      <c r="C48" s="4">
+      <c r="C48">
         <v>-98.317360411405389</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A49" s="4">
+      <c r="A49">
         <v>25</v>
       </c>
-      <c r="B49" s="4">
+      <c r="B49">
         <v>3903.6440193140625</v>
       </c>
-      <c r="C49" s="4">
+      <c r="C49">
         <v>-827.64401931406246</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A50" s="4">
+      <c r="A50">
         <v>26</v>
       </c>
-      <c r="B50" s="4">
+      <c r="B50">
         <v>6124.4692165765955</v>
       </c>
-      <c r="C50" s="4">
+      <c r="C50">
         <v>538.5307834234045</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A51" s="4">
+      <c r="A51">
         <v>27</v>
       </c>
-      <c r="B51" s="4">
+      <c r="B51">
         <v>4696.7958754792526</v>
       </c>
-      <c r="C51" s="4">
+      <c r="C51">
         <v>741.20412452074743</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A52" s="4">
+      <c r="A52">
         <v>28</v>
       </c>
-      <c r="B52" s="4">
+      <c r="B52">
         <v>3745.0136480810247</v>
       </c>
-      <c r="C52" s="4">
+      <c r="C52">
         <v>-778.01364808102471</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A53" s="4">
+      <c r="A53">
         <v>29</v>
       </c>
-      <c r="B53" s="4">
+      <c r="B53">
         <v>5965.8388453435573</v>
       </c>
-      <c r="C53" s="4">
+      <c r="C53">
         <v>-985.8388453435573</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A54" s="4">
+      <c r="A54">
         <v>30</v>
       </c>
-      <c r="B54" s="4">
+      <c r="B54">
         <v>5807.2084741105191</v>
       </c>
-      <c r="C54" s="4">
+      <c r="C54">
         <v>-45.208474110519091</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A55" s="4">
+      <c r="A55">
         <v>31</v>
       </c>
-      <c r="B55" s="4">
+      <c r="B55">
         <v>7076.2514439748238</v>
       </c>
-      <c r="C55" s="4">
+      <c r="C55">
         <v>411.74855602517619</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A56" s="4">
+      <c r="A56">
         <v>32</v>
       </c>
-      <c r="B56" s="4">
+      <c r="B56">
         <v>4855.4262467122908</v>
       </c>
-      <c r="C56" s="4">
+      <c r="C56">
         <v>-634.42624671229078</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A57" s="4">
+      <c r="A57">
         <v>33</v>
       </c>
-      <c r="B57" s="4">
+      <c r="B57">
         <v>4855.4262467122908</v>
       </c>
-      <c r="C57" s="4">
+      <c r="C57">
         <v>403.57375328770922</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A58" s="4">
+      <c r="A58">
         <v>34</v>
       </c>
-      <c r="B58" s="4">
+      <c r="B58">
         <v>4855.4262467122908</v>
       </c>
-      <c r="C58" s="4">
+      <c r="C58">
         <v>808.57375328770922</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A59" s="4">
+      <c r="A59">
         <v>35</v>
       </c>
-      <c r="B59" s="4">
+      <c r="B59">
         <v>5014.056617945329</v>
       </c>
-      <c r="C59" s="4">
+      <c r="C59">
         <v>392.94338205467102</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A60" s="4">
+      <c r="A60">
         <v>36</v>
       </c>
-      <c r="B60" s="4">
+      <c r="B60">
         <v>5014.056617945329</v>
       </c>
-      <c r="C60" s="4">
+      <c r="C60">
         <v>877.94338205467102</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A61" s="4">
+      <c r="A61">
         <v>37</v>
       </c>
-      <c r="B61" s="4">
+      <c r="B61">
         <v>3110.4921631488724</v>
       </c>
-      <c r="C61" s="4">
+      <c r="C61">
         <v>-853.49216314887235</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A62" s="4">
+      <c r="A62">
         <v>38</v>
       </c>
-      <c r="B62" s="4">
+      <c r="B62">
         <v>4696.7958754792526</v>
       </c>
-      <c r="C62" s="4">
+      <c r="C62">
         <v>-170.79587547925257</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A63" s="4">
+      <c r="A63">
         <v>39</v>
       </c>
-      <c r="B63" s="4">
+      <c r="B63">
         <v>3110.4921631488724</v>
       </c>
-      <c r="C63" s="4">
+      <c r="C63">
         <v>462.50783685112765</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A64" s="4">
+      <c r="A64">
         <v>40</v>
       </c>
-      <c r="B64" s="4">
+      <c r="B64">
         <v>3110.4921631488724</v>
       </c>
-      <c r="C64" s="4">
+      <c r="C64">
         <v>83.507836851127649</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A65" s="4">
+      <c r="A65">
         <v>41</v>
       </c>
-      <c r="B65" s="4">
+      <c r="B65">
         <v>6283.0995878096337</v>
       </c>
-      <c r="C65" s="4">
+      <c r="C65">
         <v>1761.9004121903663</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A66" s="4">
+      <c r="A66">
         <v>42</v>
       </c>
-      <c r="B66" s="4">
+      <c r="B66">
         <v>5648.5781028774818</v>
       </c>
-      <c r="C66" s="4">
+      <c r="C66">
         <v>-3.5781028774817969</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A67" s="4">
+      <c r="A67">
         <v>43</v>
       </c>
-      <c r="B67" s="4">
+      <c r="B67">
         <v>3269.1225343819106</v>
       </c>
-      <c r="C67" s="4">
+      <c r="C67">
         <v>-1330.1225343819106</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A68" s="4">
+      <c r="A68">
         <v>44</v>
       </c>
-      <c r="B68" s="4">
+      <c r="B68">
         <v>5172.6869891783672</v>
       </c>
-      <c r="C68" s="4">
+      <c r="C68">
         <v>595.31301082163282</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A69" s="4">
+      <c r="A69">
         <v>45</v>
       </c>
-      <c r="B69" s="4">
+      <c r="B69">
         <v>5807.2084741105191</v>
       </c>
-      <c r="C69" s="4">
+      <c r="C69">
         <v>1659.7915258894809</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A70" s="4">
+      <c r="A70">
         <v>46</v>
       </c>
-      <c r="B70" s="4">
+      <c r="B70">
         <v>6758.9907015087483</v>
       </c>
-      <c r="C70" s="4">
+      <c r="C70">
         <v>-288.99070150874832</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A71" s="4">
+      <c r="A71">
         <v>47</v>
       </c>
-      <c r="B71" s="4">
+      <c r="B71">
         <v>3903.6440193140625</v>
       </c>
-      <c r="C71" s="4">
+      <c r="C71">
         <v>-658.64401931406246</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A72" s="4">
+      <c r="A72">
         <v>48</v>
       </c>
-      <c r="B72" s="4">
+      <c r="B72">
         <v>3586.3832768479865</v>
       </c>
-      <c r="C72" s="4">
+      <c r="C72">
         <v>-372.38327684798651</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A73" s="4">
+      <c r="A73">
         <v>49</v>
       </c>
-      <c r="B73" s="4">
+      <c r="B73">
         <v>3586.3832768479865</v>
       </c>
-      <c r="C73" s="4">
+      <c r="C73">
         <v>-247.38327684798651</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A74" s="4">
+      <c r="A74">
         <v>50</v>
       </c>
-      <c r="B74" s="4">
+      <c r="B74">
         <v>3745.0136480810247</v>
       </c>
-      <c r="C74" s="4">
+      <c r="C74">
         <v>-146.01364808102471</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A75" s="4">
+      <c r="A75">
         <v>51</v>
       </c>
-      <c r="B75" s="4">
+      <c r="B75">
         <v>6124.4692165765955</v>
       </c>
-      <c r="C75" s="4">
+      <c r="C75">
         <v>391.5307834234045</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A76" s="4">
+      <c r="A76">
         <v>52</v>
       </c>
-      <c r="B76" s="4">
+      <c r="B76">
         <v>7234.881815207862</v>
       </c>
-      <c r="C76" s="4">
+      <c r="C76">
         <v>-139.88181520786202</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A77" s="4">
+      <c r="A77">
         <v>53</v>
       </c>
-      <c r="B77" s="4">
+      <c r="B77">
         <v>7869.4033001400139</v>
       </c>
-      <c r="C77" s="4">
+      <c r="C77">
         <v>733.59669985998607</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A78" s="4">
+      <c r="A78">
         <v>54</v>
       </c>
-      <c r="B78" s="4">
+      <c r="B78">
         <v>6917.6210727417856</v>
       </c>
-      <c r="C78" s="4">
+      <c r="C78">
         <v>167.37892725821439</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A79" s="4">
+      <c r="A79">
         <v>55</v>
       </c>
-      <c r="B79" s="4">
+      <c r="B79">
         <v>5807.2084741105191</v>
       </c>
-      <c r="C79" s="4">
+      <c r="C79">
         <v>-725.20847411051909</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A80" s="4">
+      <c r="A80">
         <v>56</v>
       </c>
-      <c r="B80" s="4">
+      <c r="B80">
         <v>3110.4921631488724</v>
       </c>
-      <c r="C80" s="4">
+      <c r="C80">
         <v>-780.49216314887235</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A81" s="4">
+      <c r="A81">
         <v>57</v>
       </c>
-      <c r="B81" s="4">
+      <c r="B81">
         <v>6441.7299590426719</v>
       </c>
-      <c r="C81" s="4">
+      <c r="C81">
         <v>-721.72995904267191</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A82" s="4">
+      <c r="A82">
         <v>58</v>
       </c>
-      <c r="B82" s="4">
+      <c r="B82">
         <v>3586.3832768479865</v>
       </c>
-      <c r="C82" s="4">
+      <c r="C82">
         <v>-898.38327684798651</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A83" s="4">
+      <c r="A83">
         <v>59</v>
       </c>
-      <c r="B83" s="4">
+      <c r="B83">
         <v>4379.5351330131771</v>
       </c>
-      <c r="C83" s="4">
+      <c r="C83">
         <v>-13.535133013177074</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A84" s="4">
+      <c r="A84">
         <v>60</v>
       </c>
-      <c r="B84" s="4">
+      <c r="B84">
         <v>4696.7958754792526</v>
       </c>
-      <c r="C84" s="4">
+      <c r="C84">
         <v>-326.79587547925257</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A85" s="4">
+      <c r="A85">
         <v>61</v>
       </c>
-      <c r="B85" s="4">
+      <c r="B85">
         <v>6124.4692165765955</v>
       </c>
-      <c r="C85" s="4">
+      <c r="C85">
         <v>89.5307834234045</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A86" s="4">
+      <c r="A86">
         <v>62</v>
       </c>
-      <c r="B86" s="4">
+      <c r="B86">
         <v>4538.1655042462153</v>
       </c>
-      <c r="C86" s="4">
+      <c r="C86">
         <v>9.8344957537847222</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A87" s="4">
+      <c r="A87">
         <v>63</v>
       </c>
-      <c r="B87" s="4">
+      <c r="B87">
         <v>3269.1225343819106</v>
       </c>
-      <c r="C87" s="4">
+      <c r="C87">
         <v>-1006.1225343819106</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A88" s="4">
+      <c r="A88">
         <v>64</v>
       </c>
-      <c r="B88" s="4">
+      <c r="B88">
         <v>3427.7529056149483</v>
       </c>
-      <c r="C88" s="4">
+      <c r="C88">
         <v>413.2470943850517</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A89" s="4">
+      <c r="A89">
         <v>65</v>
       </c>
-      <c r="B89" s="4">
+      <c r="B89">
         <v>3745.0136480810247</v>
       </c>
-      <c r="C89" s="4">
+      <c r="C89">
         <v>521.98635191897529</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A90" s="4">
+      <c r="A90">
         <v>66</v>
       </c>
-      <c r="B90" s="4">
+      <c r="B90">
         <v>8028.0336713730521</v>
       </c>
-      <c r="C90" s="4">
+      <c r="C90">
         <v>-257.03367137305213</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A91" s="4">
+      <c r="A91">
         <v>67</v>
       </c>
-      <c r="B91" s="4">
+      <c r="B91">
         <v>3269.1225343819106</v>
       </c>
-      <c r="C91" s="4">
+      <c r="C91">
         <v>152.87746561808945</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A92" s="4">
+      <c r="A92">
         <v>68</v>
       </c>
-      <c r="B92" s="4">
+      <c r="B92">
         <v>4696.7958754792526</v>
       </c>
-      <c r="C92" s="4">
+      <c r="C92">
         <v>817.20412452074743</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A93" s="4">
+      <c r="A93">
         <v>69</v>
       </c>
-      <c r="B93" s="4">
+      <c r="B93">
         <v>4696.7958754792526</v>
       </c>
-      <c r="C93" s="4">
+      <c r="C93">
         <v>-289.79587547925257</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A94" s="4">
+      <c r="A94">
         <v>70</v>
       </c>
-      <c r="B94" s="4">
+      <c r="B94">
         <v>7552.1425576739384</v>
       </c>
-      <c r="C94" s="4">
+      <c r="C94">
         <v>-690.14255767393843</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A95" s="4">
+      <c r="A95">
         <v>71</v>
       </c>
-      <c r="B95" s="4">
+      <c r="B95">
         <v>5807.2084741105191</v>
       </c>
-      <c r="C95" s="4">
+      <c r="C95">
         <v>-1115.2084741105191</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A96" s="4">
+      <c r="A96">
         <v>72</v>
       </c>
-      <c r="B96" s="4">
+      <c r="B96">
         <v>5172.6869891783672</v>
       </c>
-      <c r="C96" s="4">
+      <c r="C96">
         <v>-214.68698917836718</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A97" s="4">
+      <c r="A97">
         <v>73</v>
       </c>
-      <c r="B97" s="4">
+      <c r="B97">
         <v>4696.7958754792526</v>
       </c>
-      <c r="C97" s="4">
+      <c r="C97">
         <v>409.20412452074743</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A98" s="4">
+      <c r="A98">
         <v>74</v>
       </c>
-      <c r="B98" s="4">
+      <c r="B98">
         <v>8503.9247850721658</v>
       </c>
-      <c r="C98" s="4">
+      <c r="C98">
         <v>852.07521492783417</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A99" s="4">
+      <c r="A99">
         <v>75</v>
       </c>
-      <c r="B99" s="4">
+      <c r="B99">
         <v>6600.3603302757092</v>
       </c>
-      <c r="C99" s="4">
+      <c r="C99">
         <v>559.6396697242908</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A100" s="4">
+      <c r="A100">
         <v>76</v>
       </c>
-      <c r="B100" s="4">
+      <c r="B100">
         <v>3586.3832768479865</v>
       </c>
-      <c r="C100" s="4">
+      <c r="C100">
         <v>35.616723152013492</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A101" s="4">
+      <c r="A101">
         <v>77</v>
       </c>
-      <c r="B101" s="4">
+      <c r="B101">
         <v>6283.0995878096337</v>
       </c>
-      <c r="C101" s="4">
+      <c r="C101">
         <v>824.9004121903663</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A102" s="4">
+      <c r="A102">
         <v>78</v>
       </c>
-      <c r="B102" s="4">
+      <c r="B102">
         <v>4220.9047617801389</v>
       </c>
-      <c r="C102" s="4">
+      <c r="C102">
         <v>-143.90476178013887</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A103" s="4">
+      <c r="A103">
         <v>79</v>
       </c>
-      <c r="B103" s="4">
+      <c r="B103">
         <v>4855.4262467122908</v>
       </c>
-      <c r="C103" s="4">
+      <c r="C103">
         <v>-460.42624671229078</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A104" s="4">
+      <c r="A104">
         <v>80</v>
       </c>
-      <c r="B104" s="4">
+      <c r="B104">
         <v>5489.9477316444427</v>
       </c>
-      <c r="C104" s="4">
+      <c r="C104">
         <v>-192.94773164444268</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A105" s="4">
+      <c r="A105">
         <v>81</v>
       </c>
-      <c r="B105" s="4">
+      <c r="B105">
         <v>5965.8388453435573</v>
       </c>
-      <c r="C105" s="4">
+      <c r="C105">
         <v>-337.8388453435573</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A106" s="4">
+      <c r="A106">
         <v>82</v>
       </c>
-      <c r="B106" s="4">
+      <c r="B106">
         <v>5965.8388453435573</v>
       </c>
-      <c r="C106" s="4">
+      <c r="C106">
         <v>-350.8388453435573</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A107" s="4">
+      <c r="A107">
         <v>83</v>
       </c>
-      <c r="B107" s="4">
+      <c r="B107">
         <v>5965.8388453435573</v>
       </c>
-      <c r="C107" s="4">
+      <c r="C107">
         <v>-841.8388453435573</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A108" s="4">
+      <c r="A108">
         <v>84</v>
       </c>
-      <c r="B108" s="4">
+      <c r="B108">
         <v>3269.1225343819106</v>
       </c>
-      <c r="C108" s="4">
+      <c r="C108">
         <v>384.87746561808945</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A109" s="4">
+      <c r="A109">
         <v>85</v>
       </c>
-      <c r="B109" s="4">
+      <c r="B109">
         <v>5648.5781028774818</v>
       </c>
-      <c r="C109" s="4">
+      <c r="C109">
         <v>154.4218971225182</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A110" s="4">
+      <c r="A110">
         <v>86</v>
       </c>
-      <c r="B110" s="4">
+      <c r="B110">
         <v>5172.6869891783672</v>
       </c>
-      <c r="C110" s="4">
+      <c r="C110">
         <v>1224.3130108216328</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A111" s="4">
+      <c r="A111">
         <v>87</v>
       </c>
-      <c r="B111" s="4">
+      <c r="B111">
         <v>5014.056617945329</v>
       </c>
-      <c r="C111" s="4">
+      <c r="C111">
         <v>552.94338205467102</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A112" s="4">
+      <c r="A112">
         <v>88</v>
       </c>
-      <c r="B112" s="4">
+      <c r="B112">
         <v>7710.7729289069757</v>
       </c>
-      <c r="C112" s="4">
+      <c r="C112">
         <v>472.22707109302428</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A113" s="4">
+      <c r="A113">
         <v>89</v>
       </c>
-      <c r="B113" s="4">
+      <c r="B113">
         <v>4379.5351330131771</v>
       </c>
-      <c r="C113" s="4">
+      <c r="C113">
         <v>385.46486698682293</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A114" s="4">
+      <c r="A114">
         <v>90</v>
       </c>
-      <c r="B114" s="4">
+      <c r="B114">
         <v>3269.1225343819106</v>
       </c>
-      <c r="C114" s="4">
+      <c r="C114">
         <v>1061.8774656180894</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A115" s="4">
+      <c r="A115">
         <v>91</v>
       </c>
-      <c r="B115" s="4">
+      <c r="B115">
         <v>4062.2743905471007</v>
       </c>
-      <c r="C115" s="4">
+      <c r="C115">
         <v>-603.27439054710067</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A116" s="4">
+      <c r="A116">
         <v>92</v>
       </c>
-      <c r="B116" s="4">
+      <c r="B116">
         <v>3269.1225343819106</v>
       </c>
-      <c r="C116" s="4">
+      <c r="C116">
         <v>152.87746561808945</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A117" s="4">
+      <c r="A117">
         <v>93</v>
       </c>
-      <c r="B117" s="4">
+      <c r="B117">
         <v>5648.5781028774818</v>
       </c>
-      <c r="C117" s="4">
+      <c r="C117">
         <v>-293.5781028774818</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A118" s="4">
+      <c r="A118">
         <v>94</v>
       </c>
-      <c r="B118" s="4">
+      <c r="B118">
         <v>3269.1225343819106</v>
       </c>
-      <c r="C118" s="4">
+      <c r="C118">
         <v>-683.12253438191055</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A119" s="4">
+      <c r="A119">
         <v>95</v>
       </c>
-      <c r="B119" s="4">
+      <c r="B119">
         <v>4538.1655042462153</v>
       </c>
-      <c r="C119" s="4">
+      <c r="C119">
         <v>-126.16550424621528</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A120" s="4">
+      <c r="A120">
         <v>96</v>
       </c>
-      <c r="B120" s="4">
+      <c r="B120">
         <v>3586.3832768479865</v>
       </c>
-      <c r="C120" s="4">
+      <c r="C120">
         <v>378.61672315201349</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A121" s="4">
+      <c r="A121">
         <v>97</v>
       </c>
-      <c r="B121" s="4">
+      <c r="B121">
         <v>5965.8388453435573</v>
       </c>
-      <c r="C121" s="4">
+      <c r="C121">
         <v>548.1611546564427</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A122" s="4">
+      <c r="A122">
         <v>98</v>
       </c>
-      <c r="B122" s="4">
+      <c r="B122">
         <v>5014.056617945329</v>
       </c>
-      <c r="C122" s="4">
+      <c r="C122">
         <v>463.94338205467102</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A123" s="4">
+      <c r="A123">
         <v>99</v>
       </c>
-      <c r="B123" s="4">
+      <c r="B123">
         <v>3110.4921631488724</v>
       </c>
-      <c r="C123" s="4">
+      <c r="C123">
         <v>505.50783685112765</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A124" s="4">
+      <c r="A124">
         <v>100</v>
       </c>
-      <c r="B124" s="4">
+      <c r="B124">
         <v>4855.4262467122908</v>
       </c>
-      <c r="C124" s="4">
+      <c r="C124">
         <v>664.57375328770922</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A125" s="4">
+      <c r="A125">
         <v>101</v>
       </c>
-      <c r="B125" s="4">
+      <c r="B125">
         <v>4220.9047617801389</v>
       </c>
-      <c r="C125" s="4">
+      <c r="C125">
         <v>135.09523821986113</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A126" s="4">
+      <c r="A126">
         <v>102</v>
       </c>
-      <c r="B126" s="4">
+      <c r="B126">
         <v>3110.4921631488724</v>
       </c>
-      <c r="C126" s="4">
+      <c r="C126">
         <v>58.507836851127649</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A127" s="4">
+      <c r="A127">
         <v>103</v>
       </c>
-      <c r="B127" s="4">
+      <c r="B127">
         <v>3427.7529056149483</v>
       </c>
-      <c r="C127" s="4">
+      <c r="C127">
         <v>-53.752905614948304</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A128" s="4">
+      <c r="A128">
         <v>104</v>
       </c>
-      <c r="B128" s="4">
+      <c r="B128">
         <v>4696.7958754792526</v>
       </c>
-      <c r="C128" s="4">
+      <c r="C128">
         <v>-84.795875479252572</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A129" s="4">
+      <c r="A129">
         <v>105</v>
       </c>
-      <c r="B129" s="4">
+      <c r="B129">
         <v>7552.1425576739384</v>
       </c>
-      <c r="C129" s="4">
+      <c r="C129">
         <v>449.85744232606157</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A130" s="4">
+      <c r="A130">
         <v>106</v>
       </c>
-      <c r="B130" s="4">
+      <c r="B130">
         <v>3269.1225343819106</v>
       </c>
-      <c r="C130" s="4">
+      <c r="C130">
         <v>-341.12253438191055</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A131" s="4">
+      <c r="A131">
         <v>107</v>
       </c>
-      <c r="B131" s="4">
+      <c r="B131">
         <v>3110.4921631488724</v>
       </c>
-      <c r="C131" s="4">
+      <c r="C131">
         <v>-67.492163148872351</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A132" s="4">
+      <c r="A132">
         <v>108</v>
       </c>
-      <c r="B132" s="4">
+      <c r="B132">
         <v>3269.1225343819106</v>
       </c>
-      <c r="C132" s="4">
+      <c r="C132">
         <v>-352.12253438191055</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A133" s="4">
+      <c r="A133">
         <v>109</v>
       </c>
-      <c r="B133" s="4">
+      <c r="B133">
         <v>3903.6440193140625</v>
       </c>
-      <c r="C133" s="4">
+      <c r="C133">
         <v>886.35598068593754</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A134" s="4">
+      <c r="A134">
         <v>110</v>
       </c>
-      <c r="B134" s="4">
+      <c r="B134">
         <v>4538.1655042462153</v>
       </c>
-      <c r="C134" s="4">
+      <c r="C134">
         <v>792.83449575378472</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A135" s="4">
+      <c r="A135">
         <v>111</v>
       </c>
-      <c r="B135" s="4">
+      <c r="B135">
         <v>4855.4262467122908</v>
       </c>
-      <c r="C135" s="4">
+      <c r="C135">
         <v>413.57375328770922</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A136" s="4">
+      <c r="A136">
         <v>112</v>
       </c>
-      <c r="B136" s="4">
+      <c r="B136">
         <v>3269.1225343819106</v>
       </c>
-      <c r="C136" s="4">
+      <c r="C136">
         <v>860.87746561808945</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A137" s="4">
+      <c r="A137">
         <v>113</v>
       </c>
-      <c r="B137" s="4">
+      <c r="B137">
         <v>6283.0995878096337</v>
       </c>
-      <c r="C137" s="4">
+      <c r="C137">
         <v>-484.0995878096337</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A138" s="4">
+      <c r="A138">
         <v>114</v>
       </c>
-      <c r="B138" s="4">
+      <c r="B138">
         <v>4538.1655042462153</v>
       </c>
-      <c r="C138" s="4">
+      <c r="C138">
         <v>351.83449575378472</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A139" s="4">
+      <c r="A139">
         <v>115</v>
       </c>
-      <c r="B139" s="4">
+      <c r="B139">
         <v>5648.5781028774818</v>
       </c>
-      <c r="C139" s="4">
+      <c r="C139">
         <v>-822.5781028774818</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A140" s="4">
+      <c r="A140">
         <v>116</v>
       </c>
-      <c r="B140" s="4">
+      <c r="B140">
         <v>8345.2944138391285</v>
       </c>
-      <c r="C140" s="4">
+      <c r="C140">
         <v>-323.29441383912854</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A141" s="4">
+      <c r="A141">
         <v>117</v>
       </c>
-      <c r="B141" s="4">
+      <c r="B141">
         <v>3745.0136480810247</v>
       </c>
-      <c r="C141" s="4">
+      <c r="C141">
         <v>-105.01364808102471</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A142" s="4">
+      <c r="A142">
         <v>118</v>
       </c>
-      <c r="B142" s="4">
+      <c r="B142">
         <v>3427.7529056149483</v>
       </c>
-      <c r="C142" s="4">
+      <c r="C142">
         <v>561.2470943850517</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A143" s="4">
+      <c r="A143">
         <v>119</v>
       </c>
-      <c r="B143" s="4">
+      <c r="B143">
         <v>3903.6440193140625</v>
       </c>
-      <c r="C143" s="4">
+      <c r="C143">
         <v>-1038.6440193140625</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A144" s="4">
+      <c r="A144">
         <v>120</v>
       </c>
-      <c r="B144" s="4">
+      <c r="B144">
         <v>8345.2944138391285</v>
       </c>
-      <c r="C144" s="4">
+      <c r="C144">
         <v>273.70558616087146</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A145" s="4">
+      <c r="A145">
         <v>121</v>
       </c>
-      <c r="B145" s="4">
+      <c r="B145">
         <v>3269.1225343819106</v>
       </c>
-      <c r="C145" s="4">
+      <c r="C145">
         <v>74.877465618089445</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A146" s="4">
+      <c r="A146">
         <v>122</v>
       </c>
-      <c r="B146" s="4">
+      <c r="B146">
         <v>7552.1425576739384</v>
       </c>
-      <c r="C146" s="4">
+      <c r="C146">
         <v>1163.8574423260616</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A147" s="4">
+      <c r="A147">
         <v>123</v>
       </c>
-      <c r="B147" s="4">
+      <c r="B147">
         <v>5014.056617945329</v>
       </c>
-      <c r="C147" s="4">
+      <c r="C147">
         <v>-304.05661794532898</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A148" s="4">
+      <c r="A148">
         <v>124</v>
       </c>
-      <c r="B148" s="4">
+      <c r="B148">
         <v>3745.0136480810247</v>
       </c>
-      <c r="C148" s="4">
+      <c r="C148">
         <v>98.986351918975288</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A149" s="4">
+      <c r="A149">
         <v>125</v>
       </c>
-      <c r="B149" s="4">
+      <c r="B149">
         <v>6758.9907015087483</v>
       </c>
-      <c r="C149" s="4">
+      <c r="C149">
         <v>-589.99070150874832</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A150" s="4">
+      <c r="A150">
         <v>126</v>
       </c>
-      <c r="B150" s="4">
+      <c r="B150">
         <v>5489.9477316444427</v>
       </c>
-      <c r="C150" s="4">
+      <c r="C150">
         <v>978.05226835555732</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A151" s="4">
+      <c r="A151">
         <v>127</v>
       </c>
-      <c r="B151" s="4">
+      <c r="B151">
         <v>8345.2944138391285</v>
       </c>
-      <c r="C151" s="4">
+      <c r="C151">
         <v>-987.29441383912854</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A152" s="4">
+      <c r="A152">
         <v>128</v>
       </c>
-      <c r="B152" s="4">
+      <c r="B152">
         <v>3269.1225343819106</v>
       </c>
-      <c r="C152" s="4">
+      <c r="C152">
         <v>1398.8774656180894</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A153" s="4">
+      <c r="A153">
         <v>129</v>
       </c>
-      <c r="B153" s="4">
+      <c r="B153">
         <v>4696.7958754792526</v>
       </c>
-      <c r="C153" s="4">
+      <c r="C153">
         <v>898.20412452074743</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A154" s="4">
+      <c r="A154">
         <v>130</v>
       </c>
-      <c r="B154" s="4">
+      <c r="B154">
         <v>3269.1225343819106</v>
       </c>
-      <c r="C154" s="4">
+      <c r="C154">
         <v>76.877465618089445</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A155" s="4">
+      <c r="A155">
         <v>131</v>
       </c>
-      <c r="B155" s="4">
+      <c r="B155">
         <v>3745.0136480810247</v>
       </c>
-      <c r="C155" s="4">
+      <c r="C155">
         <v>126.98635191897529</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A156" s="4">
+      <c r="A156">
         <v>132</v>
       </c>
-      <c r="B156" s="4">
+      <c r="B156">
         <v>3269.1225343819106</v>
       </c>
-      <c r="C156" s="4">
+      <c r="C156">
         <v>-372.12253438191055</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A157" s="4">
+      <c r="A157">
         <v>133</v>
       </c>
-      <c r="B157" s="4">
+      <c r="B157">
         <v>3745.0136480810247</v>
       </c>
-      <c r="C157" s="4">
+      <c r="C157">
         <v>-390.01364808102471</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A158" s="4">
+      <c r="A158">
         <v>134</v>
       </c>
-      <c r="B158" s="4">
+      <c r="B158">
         <v>4696.7958754792526</v>
       </c>
-      <c r="C158" s="4">
+      <c r="C158">
         <v>272.20412452074743</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A159" s="4">
+      <c r="A159">
         <v>135</v>
       </c>
-      <c r="B159" s="4">
+      <c r="B159">
         <v>4379.5351330131771</v>
       </c>
-      <c r="C159" s="4">
+      <c r="C159">
         <v>-647.53513301317707</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A160" s="4">
+      <c r="A160">
         <v>136</v>
       </c>
-      <c r="B160" s="4">
+      <c r="B160">
         <v>4855.4262467122908</v>
       </c>
-      <c r="C160" s="4">
+      <c r="C160">
         <v>1066.5737532877092</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A161" s="4">
+      <c r="A161">
         <v>137</v>
       </c>
-      <c r="B161" s="4">
+      <c r="B161">
         <v>3110.4921631488724</v>
       </c>
-      <c r="C161" s="4">
+      <c r="C161">
         <v>-121.49216314887235</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A162" s="4">
+      <c r="A162">
         <v>138</v>
       </c>
-      <c r="B162" s="4">
+      <c r="B162">
         <v>3427.7529056149483</v>
       </c>
-      <c r="C162" s="4">
+      <c r="C162">
         <v>1057.2470943850517</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A163" s="4">
+      <c r="A163">
         <v>139</v>
       </c>
-      <c r="B163" s="4">
+      <c r="B163">
         <v>4220.9047617801389</v>
       </c>
-      <c r="C163" s="4">
+      <c r="C163">
         <v>47.09523821986113</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A164" s="4">
+      <c r="A164">
         <v>140</v>
       </c>
-      <c r="B164" s="4">
+      <c r="B164">
         <v>4538.1655042462153</v>
       </c>
-      <c r="C164" s="4">
+      <c r="C164">
         <v>-1350.1655042462153</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A165" s="4">
+      <c r="A165">
         <v>141</v>
       </c>
-      <c r="B165" s="4">
+      <c r="B165">
         <v>4855.4262467122908</v>
       </c>
-      <c r="C165" s="4">
+      <c r="C165">
         <v>981.57375328770922</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A166" s="4">
+      <c r="A166">
         <v>142</v>
       </c>
-      <c r="B166" s="4">
+      <c r="B166">
         <v>5014.056617945329</v>
       </c>
-      <c r="C166" s="4">
+      <c r="C166">
         <v>-870.05661794532898</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A167" s="4">
+      <c r="A167">
         <v>143</v>
       </c>
-      <c r="B167" s="4">
+      <c r="B167">
         <v>3110.4921631488724</v>
       </c>
-      <c r="C167" s="4">
+      <c r="C167">
         <v>156.50783685112765</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A168" s="4">
+      <c r="A168">
         <v>144</v>
       </c>
-      <c r="B168" s="4">
+      <c r="B168">
         <v>3586.3832768479865</v>
       </c>
-      <c r="C168" s="4">
+      <c r="C168">
         <v>205.61672315201349</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A169" s="4">
+      <c r="A169">
         <v>145</v>
       </c>
-      <c r="B169" s="4">
+      <c r="B169">
         <v>4538.1655042462153</v>
       </c>
-      <c r="C169" s="4">
+      <c r="C169">
         <v>-182.16550424621528</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A170" s="4">
+      <c r="A170">
         <v>146</v>
       </c>
-      <c r="B170" s="4">
+      <c r="B170">
         <v>5807.2084741105191</v>
       </c>
-      <c r="C170" s="4">
+      <c r="C170">
         <v>-648.20847411051909</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A171" s="4">
+      <c r="A171">
         <v>147</v>
       </c>
-      <c r="B171" s="4">
+      <c r="B171">
         <v>3427.7529056149483</v>
       </c>
-      <c r="C171" s="4">
+      <c r="C171">
         <v>-182.7529056149483</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A172" s="4">
+      <c r="A172">
         <v>148</v>
       </c>
-      <c r="B172" s="4">
+      <c r="B172">
         <v>5965.8388453435573</v>
       </c>
-      <c r="C172" s="4">
+      <c r="C172">
         <v>728.1611546564427</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A173" s="4">
+      <c r="A173">
         <v>149</v>
       </c>
-      <c r="B173" s="4">
+      <c r="B173">
         <v>4062.2743905471007</v>
       </c>
-      <c r="C173" s="4">
+      <c r="C173">
         <v>17.725609452899334</v>
       </c>
     </row>
     <row r="174" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A174" s="5">
+      <c r="A174" s="4">
         <v>150</v>
       </c>
-      <c r="B174" s="5">
+      <c r="B174" s="4">
         <v>3586.3832768479865</v>
       </c>
-      <c r="C174" s="5">
+      <c r="C174" s="4">
         <v>-587.38327684798651</v>
       </c>
     </row>
@@ -20196,7 +22290,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00ADB2C1-F40C-4473-8A54-B4932D72BE76}">
   <dimension ref="A1:I177"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -20218,48 +22312,48 @@
     </row>
     <row r="2" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="B3" s="7"/>
+      <c r="B3" s="3"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
+      <c r="A4" t="s">
         <v>90</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4">
         <v>0.95744492552625793</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
+      <c r="A5" t="s">
         <v>91</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5">
         <v>0.91670078541598154</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6" s="4" t="s">
+      <c r="A6" t="s">
         <v>92</v>
       </c>
-      <c r="B6" s="4">
+      <c r="B6">
         <v>0.91440287604814663</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7" s="4" t="s">
+      <c r="A7" t="s">
         <v>93</v>
       </c>
-      <c r="B7" s="4">
+      <c r="B7">
         <v>467.82761551452887</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="B8" s="5">
+      <c r="B8" s="4">
         <v>150</v>
       </c>
     </row>
@@ -20269,243 +22363,241 @@
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A11" s="6"/>
-      <c r="B11" s="6" t="s">
+      <c r="A11" s="5"/>
+      <c r="B11" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="E11" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="F11" s="6" t="s">
+      <c r="F11" s="5" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A12" s="4" t="s">
+      <c r="A12" t="s">
         <v>96</v>
       </c>
-      <c r="B12" s="4">
+      <c r="B12">
         <v>4</v>
       </c>
-      <c r="C12" s="4">
+      <c r="C12">
         <v>349241952.67348874</v>
       </c>
-      <c r="D12" s="4">
+      <c r="D12">
         <v>87310488.168372184</v>
       </c>
-      <c r="E12" s="4">
+      <c r="E12">
         <v>398.92817281982911</v>
       </c>
-      <c r="F12" s="4">
+      <c r="F12">
         <v>3.7628530221554506E-77</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A13" s="4" t="s">
+      <c r="A13" t="s">
         <v>97</v>
       </c>
-      <c r="B13" s="4">
+      <c r="B13">
         <v>145</v>
       </c>
-      <c r="C13" s="4">
+      <c r="C13">
         <v>31735088.286511432</v>
       </c>
-      <c r="D13" s="4">
+      <c r="D13">
         <v>218862.67783800987</v>
       </c>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
     </row>
     <row r="14" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="B14" s="5">
+      <c r="B14" s="4">
         <v>149</v>
       </c>
-      <c r="C14" s="5">
+      <c r="C14" s="4">
         <v>380977040.96000016</v>
       </c>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
     </row>
     <row r="15" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A16" s="6"/>
-      <c r="B16" s="6" t="s">
+      <c r="A16" s="5"/>
+      <c r="B16" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="D16" s="6" t="s">
+      <c r="D16" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="E16" s="6" t="s">
+      <c r="E16" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="F16" s="6" t="s">
+      <c r="F16" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="G16" s="6" t="s">
+      <c r="G16" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="H16" s="6" t="s">
+      <c r="H16" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="I16" s="6" t="s">
+      <c r="I16" s="5" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A17" s="4" t="s">
+      <c r="A17" t="s">
         <v>99</v>
       </c>
-      <c r="B17" s="4">
+      <c r="B17">
         <v>1493.8615163253114</v>
       </c>
-      <c r="C17" s="4">
+      <c r="C17">
         <v>234.29287532119923</v>
       </c>
-      <c r="D17" s="4">
+      <c r="D17">
         <v>6.3760432931532005</v>
       </c>
-      <c r="E17" s="4">
+      <c r="E17">
         <v>2.2827925586494613E-9</v>
       </c>
-      <c r="F17" s="4">
+      <c r="F17">
         <v>1030.7911224399659</v>
       </c>
-      <c r="G17" s="4">
+      <c r="G17">
         <v>1956.931910210657</v>
       </c>
-      <c r="H17" s="4">
+      <c r="H17">
         <v>1030.7911224399659</v>
       </c>
-      <c r="I17" s="4">
+      <c r="I17">
         <v>1956.931910210657</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A18" s="4" t="s">
+      <c r="A18" t="s">
         <v>1</v>
       </c>
-      <c r="B18" s="4">
+      <c r="B18">
         <v>15.029679257828146</v>
       </c>
-      <c r="C18" s="4">
+      <c r="C18">
         <v>4.8051815348709361</v>
       </c>
-      <c r="D18" s="4">
+      <c r="D18">
         <v>3.1278067537633274</v>
       </c>
-      <c r="E18" s="4">
+      <c r="E18">
         <v>2.1289940868917992E-3</v>
       </c>
-      <c r="F18" s="4">
+      <c r="F18">
         <v>5.5324322630453757</v>
       </c>
-      <c r="G18" s="4">
+      <c r="G18">
         <v>24.526926252610917</v>
       </c>
-      <c r="H18" s="4">
+      <c r="H18">
         <v>5.5324322630453757</v>
       </c>
-      <c r="I18" s="4">
+      <c r="I18">
         <v>24.526926252610917</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A19" s="4" t="s">
+      <c r="A19" t="s">
         <v>2</v>
       </c>
-      <c r="B19" s="4">
+      <c r="B19">
         <v>148.85252631957565</v>
       </c>
-      <c r="C19" s="4">
+      <c r="C19">
         <v>5.3528303843903986</v>
       </c>
-      <c r="D19" s="4">
+      <c r="D19">
         <v>27.808190364792878</v>
       </c>
-      <c r="E19" s="4">
+      <c r="E19">
         <v>5.4982854924289446E-60</v>
       </c>
-      <c r="F19" s="4">
+      <c r="F19">
         <v>138.27287351919523</v>
       </c>
-      <c r="G19" s="4">
+      <c r="G19">
         <v>159.43217911995606</v>
       </c>
-      <c r="H19" s="4">
+      <c r="H19">
         <v>138.27287351919523</v>
       </c>
-      <c r="I19" s="4">
+      <c r="I19">
         <v>159.43217911995606</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A20" s="4" t="s">
+      <c r="A20" t="s">
         <v>3</v>
       </c>
-      <c r="B20" s="4">
+      <c r="B20">
         <v>548.72052044711074</v>
       </c>
-      <c r="C20" s="4">
+      <c r="C20">
         <v>49.182191598515566</v>
       </c>
-      <c r="D20" s="4">
+      <c r="D20">
         <v>11.156894449243543</v>
       </c>
-      <c r="E20" s="4">
+      <c r="E20">
         <v>2.959964854441944E-21</v>
       </c>
-      <c r="F20" s="4">
+      <c r="F20">
         <v>451.51390755098043</v>
       </c>
-      <c r="G20" s="4">
+      <c r="G20">
         <v>645.92713334324105</v>
       </c>
-      <c r="H20" s="4">
+      <c r="H20">
         <v>451.51390755098043</v>
       </c>
-      <c r="I20" s="4">
+      <c r="I20">
         <v>645.92713334324105</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B21" s="5">
+      <c r="B21" s="4">
         <v>9.3973956620239125</v>
       </c>
-      <c r="C21" s="5">
+      <c r="C21" s="4">
         <v>5.4009246148100907</v>
       </c>
-      <c r="D21" s="5">
+      <c r="D21" s="4">
         <v>1.7399605312495825</v>
       </c>
-      <c r="E21" s="5">
+      <c r="E21" s="4">
         <v>8.3987697642079986E-2</v>
       </c>
-      <c r="F21" s="5">
+      <c r="F21" s="4">
         <v>-1.2773134399769841</v>
       </c>
-      <c r="G21" s="5">
+      <c r="G21" s="4">
         <v>20.072104764024807</v>
       </c>
-      <c r="H21" s="5">
+      <c r="H21" s="4">
         <v>-1.2773134399769841</v>
       </c>
-      <c r="I21" s="5">
+      <c r="I21" s="4">
         <v>20.072104764024807</v>
       </c>
     </row>
@@ -20516,1663 +22608,1663 @@
     </row>
     <row r="26" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A27" s="6" t="s">
+      <c r="A27" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="B27" s="6" t="s">
+      <c r="B27" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="C27" s="6" t="s">
+      <c r="C27" s="5" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A28" s="4">
+      <c r="A28">
         <v>1</v>
       </c>
-      <c r="B28" s="4">
+      <c r="B28">
         <v>3698.0499197499707</v>
       </c>
-      <c r="C28" s="4">
+      <c r="C28">
         <v>82.950080250029259</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A29" s="4">
+      <c r="A29">
         <v>2</v>
       </c>
-      <c r="B29" s="4">
+      <c r="B29">
         <v>3789.4364060908192</v>
       </c>
-      <c r="C29" s="4">
+      <c r="C29">
         <v>225.56359390918078</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A30" s="4">
+      <c r="A30">
         <v>3</v>
       </c>
-      <c r="B30" s="4">
+      <c r="B30">
         <v>3639.8291432552933</v>
       </c>
-      <c r="C30" s="4">
+      <c r="C30">
         <v>-389.82914325529327</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A31" s="4">
+      <c r="A31">
         <v>4</v>
       </c>
-      <c r="B31" s="4">
+      <c r="B31">
         <v>5814.0077940495157</v>
       </c>
-      <c r="C31" s="4">
+      <c r="C31">
         <v>502.99220595048428</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A32" s="4">
+      <c r="A32">
         <v>5</v>
       </c>
-      <c r="B32" s="4">
+      <c r="B32">
         <v>5651.9927600016963</v>
       </c>
-      <c r="C32" s="4">
+      <c r="C32">
         <v>-785.9927600016963</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A33" s="4">
+      <c r="A33">
         <v>6</v>
       </c>
-      <c r="B33" s="4">
+      <c r="B33">
         <v>3613.5385655649493</v>
       </c>
-      <c r="C33" s="4">
+      <c r="C33">
         <v>-132.53856556494929</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A34" s="4">
+      <c r="A34">
         <v>7</v>
       </c>
-      <c r="B34" s="4">
+      <c r="B34">
         <v>5275.9382169579894</v>
       </c>
-      <c r="C34" s="4">
+      <c r="C34">
         <v>266.06178304201057</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A35" s="4">
+      <c r="A35">
         <v>8</v>
       </c>
-      <c r="B35" s="4">
+      <c r="B35">
         <v>6126.2888516685662</v>
       </c>
-      <c r="C35" s="4">
+      <c r="C35">
         <v>-113.28885166856617</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A36" s="4">
+      <c r="A36">
         <v>9</v>
       </c>
-      <c r="B36" s="4">
+      <c r="B36">
         <v>6157.4606451978561</v>
       </c>
-      <c r="C36" s="4">
+      <c r="C36">
         <v>-436.46064519785614</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A37" s="4">
+      <c r="A37">
         <v>10</v>
       </c>
-      <c r="B37" s="4">
+      <c r="B37">
         <v>5766.9900467323459</v>
       </c>
-      <c r="C37" s="4">
+      <c r="C37">
         <v>140.00995326765405</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A38" s="4">
+      <c r="A38">
         <v>11</v>
       </c>
-      <c r="B38" s="4">
+      <c r="B38">
         <v>3304.5689457341896</v>
       </c>
-      <c r="C38" s="4">
+      <c r="C38">
         <v>-199.56894573418958</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A39" s="4">
+      <c r="A39">
         <v>12</v>
       </c>
-      <c r="B39" s="4">
+      <c r="B39">
         <v>4790.7733631224328</v>
       </c>
-      <c r="C39" s="4">
+      <c r="C39">
         <v>-299.77336312243278</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A40" s="4">
+      <c r="A40">
         <v>13</v>
       </c>
-      <c r="B40" s="4">
+      <c r="B40">
         <v>3813.5353185246927</v>
       </c>
-      <c r="C40" s="4">
+      <c r="C40">
         <v>443.46468147530732</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A41" s="4">
+      <c r="A41">
         <v>14</v>
       </c>
-      <c r="B41" s="4">
+      <c r="B41">
         <v>7932.3956248341046</v>
       </c>
-      <c r="C41" s="4">
+      <c r="C41">
         <v>215.60437516589536</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A42" s="4">
+      <c r="A42">
         <v>15</v>
       </c>
-      <c r="B42" s="4">
+      <c r="B42">
         <v>7149.853880845375</v>
       </c>
-      <c r="C42" s="4">
+      <c r="C42">
         <v>-414.85388084537499</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A43" s="4">
+      <c r="A43">
         <v>16</v>
       </c>
-      <c r="B43" s="4">
+      <c r="B43">
         <v>2623.5609185098447</v>
       </c>
-      <c r="C43" s="4">
+      <c r="C43">
         <v>-305.56091850984467</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A44" s="4">
+      <c r="A44">
         <v>17</v>
       </c>
-      <c r="B44" s="4">
+      <c r="B44">
         <v>7197.5303888982507</v>
       </c>
-      <c r="C44" s="4">
+      <c r="C44">
         <v>-275.53038889825075</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A45" s="4">
+      <c r="A45">
         <v>18</v>
       </c>
-      <c r="B45" s="4">
+      <c r="B45">
         <v>3275.2606549753909</v>
       </c>
-      <c r="C45" s="4">
+      <c r="C45">
         <v>-707.26065497539093</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A46" s="4">
+      <c r="A46">
         <v>19</v>
       </c>
-      <c r="B46" s="4">
+      <c r="B46">
         <v>4778.4566659359461</v>
       </c>
-      <c r="C46" s="4">
+      <c r="C46">
         <v>-68.456665935946148</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A47" s="4">
+      <c r="A47">
         <v>20</v>
       </c>
-      <c r="B47" s="4">
+      <c r="B47">
         <v>7464.4865532789909</v>
       </c>
-      <c r="C47" s="4">
+      <c r="C47">
         <v>-363.48655327899087</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A48" s="4">
+      <c r="A48">
         <v>21</v>
       </c>
-      <c r="B48" s="4">
+      <c r="B48">
         <v>7617.0734226577351</v>
       </c>
-      <c r="C48" s="4">
+      <c r="C48">
         <v>-925.07342265773514</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A49" s="4">
+      <c r="A49">
         <v>22</v>
       </c>
-      <c r="B49" s="4">
+      <c r="B49">
         <v>4540.0552887934009</v>
       </c>
-      <c r="C49" s="4">
+      <c r="C49">
         <v>-232.0552887934009</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A50" s="4">
+      <c r="A50">
         <v>23</v>
       </c>
-      <c r="B50" s="4">
+      <c r="B50">
         <v>2870.152513515879</v>
       </c>
-      <c r="C50" s="4">
+      <c r="C50">
         <v>248.84748648412096</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A51" s="4">
+      <c r="A51">
         <v>24</v>
       </c>
-      <c r="B51" s="4">
+      <c r="B51">
         <v>5015.2587290161291</v>
       </c>
-      <c r="C51" s="4">
+      <c r="C51">
         <v>217.74127098387089</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A52" s="4">
+      <c r="A52">
         <v>25</v>
       </c>
-      <c r="B52" s="4">
+      <c r="B52">
         <v>3350.5037940494317</v>
       </c>
-      <c r="C52" s="4">
+      <c r="C52">
         <v>-274.50379404943169</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A53" s="4">
+      <c r="A53">
         <v>26</v>
       </c>
-      <c r="B53" s="4">
+      <c r="B53">
         <v>6900.091960730977</v>
       </c>
-      <c r="C53" s="4">
+      <c r="C53">
         <v>-237.09196073097701</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A54" s="4">
+      <c r="A54">
         <v>27</v>
       </c>
-      <c r="B54" s="4">
+      <c r="B54">
         <v>5276.7532584926957</v>
       </c>
-      <c r="C54" s="4">
+      <c r="C54">
         <v>161.24674150730425</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A55" s="4">
+      <c r="A55">
         <v>28</v>
       </c>
-      <c r="B55" s="4">
+      <c r="B55">
         <v>3352.0095983222386</v>
       </c>
-      <c r="C55" s="4">
+      <c r="C55">
         <v>-385.00959832223862</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A56" s="4">
+      <c r="A56">
         <v>29</v>
       </c>
-      <c r="B56" s="4">
+      <c r="B56">
         <v>6031.5601585323757</v>
       </c>
-      <c r="C56" s="4">
+      <c r="C56">
         <v>-1051.5601585323757</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A57" s="4">
+      <c r="A57">
         <v>30</v>
       </c>
-      <c r="B57" s="4">
+      <c r="B57">
         <v>6008.6388878853313</v>
       </c>
-      <c r="C57" s="4">
+      <c r="C57">
         <v>-246.63888788533131</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A58" s="4">
+      <c r="A58">
         <v>31</v>
       </c>
-      <c r="B58" s="4">
+      <c r="B58">
         <v>7845.8879185684555</v>
       </c>
-      <c r="C58" s="4">
+      <c r="C58">
         <v>-357.88791856845546</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A59" s="4">
+      <c r="A59">
         <v>32</v>
       </c>
-      <c r="B59" s="4">
+      <c r="B59">
         <v>4728.395338297707</v>
       </c>
-      <c r="C59" s="4">
+      <c r="C59">
         <v>-507.39533829770699</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A60" s="4">
+      <c r="A60">
         <v>33</v>
       </c>
-      <c r="B60" s="4">
+      <c r="B60">
         <v>5560.9036671397753</v>
       </c>
-      <c r="C60" s="4">
+      <c r="C60">
         <v>-301.90366713977528</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A61" s="4">
+      <c r="A61">
         <v>34</v>
       </c>
-      <c r="B61" s="4">
+      <c r="B61">
         <v>5795.7770206762725</v>
       </c>
-      <c r="C61" s="4">
+      <c r="C61">
         <v>-131.77702067627251</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A62" s="4">
+      <c r="A62">
         <v>35</v>
       </c>
-      <c r="B62" s="4">
+      <c r="B62">
         <v>4839.6275129621372</v>
       </c>
-      <c r="C62" s="4">
+      <c r="C62">
         <v>567.37248703786281</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A63" s="4">
+      <c r="A63">
         <v>36</v>
       </c>
-      <c r="B63" s="4">
+      <c r="B63">
         <v>5689.0634615986683</v>
       </c>
-      <c r="C63" s="4">
+      <c r="C63">
         <v>202.93653840133175</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A64" s="4">
+      <c r="A64">
         <v>37</v>
       </c>
-      <c r="B64" s="4">
+      <c r="B64">
         <v>2476.6063327269044</v>
       </c>
-      <c r="C64" s="4">
+      <c r="C64">
         <v>-219.60633272690438</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A65" s="4">
+      <c r="A65">
         <v>38</v>
       </c>
-      <c r="B65" s="4">
+      <c r="B65">
         <v>4143.6205754870134</v>
       </c>
-      <c r="C65" s="4">
+      <c r="C65">
         <v>382.37942451298659</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A66" s="4">
+      <c r="A66">
         <v>39</v>
       </c>
-      <c r="B66" s="4">
+      <c r="B66">
         <v>3177.5523552959821</v>
       </c>
-      <c r="C66" s="4">
+      <c r="C66">
         <v>395.44764470401788</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A67" s="4">
+      <c r="A67">
         <v>40</v>
       </c>
-      <c r="B67" s="4">
+      <c r="B67">
         <v>3034.7242488360394</v>
       </c>
-      <c r="C67" s="4">
+      <c r="C67">
         <v>159.27575116396065</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A68" s="4">
+      <c r="A68">
         <v>41</v>
       </c>
-      <c r="B68" s="4">
+      <c r="B68">
         <v>6620.5229386801675</v>
       </c>
-      <c r="C68" s="4">
+      <c r="C68">
         <v>1424.4770613198325</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A69" s="4">
+      <c r="A69">
         <v>42</v>
       </c>
-      <c r="B69" s="4">
+      <c r="B69">
         <v>5794.0353609386384</v>
       </c>
-      <c r="C69" s="4">
+      <c r="C69">
         <v>-149.03536093863841</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A70" s="4">
+      <c r="A70">
         <v>43</v>
       </c>
-      <c r="B70" s="4">
+      <c r="B70">
         <v>2710.0046509976446</v>
       </c>
-      <c r="C70" s="4">
+      <c r="C70">
         <v>-771.0046509976446</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A71" s="4">
+      <c r="A71">
         <v>44</v>
       </c>
-      <c r="B71" s="4">
+      <c r="B71">
         <v>5212.1798996524085</v>
       </c>
-      <c r="C71" s="4">
+      <c r="C71">
         <v>555.82010034759151</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A72" s="4">
+      <c r="A72">
         <v>45</v>
       </c>
-      <c r="B72" s="4">
+      <c r="B72">
         <v>6655.0677080118503</v>
       </c>
-      <c r="C72" s="4">
+      <c r="C72">
         <v>811.9322919881497</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A73" s="4">
+      <c r="A73">
         <v>46</v>
       </c>
-      <c r="B73" s="4">
+      <c r="B73">
         <v>6351.1355848190406</v>
       </c>
-      <c r="C73" s="4">
+      <c r="C73">
         <v>118.86441518095944</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A74" s="4">
+      <c r="A74">
         <v>47</v>
       </c>
-      <c r="B74" s="4">
+      <c r="B74">
         <v>3675.5244541258467</v>
       </c>
-      <c r="C74" s="4">
+      <c r="C74">
         <v>-430.52445412584666</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A75" s="4">
+      <c r="A75">
         <v>48</v>
       </c>
-      <c r="B75" s="4">
+      <c r="B75">
         <v>3158.0680342291785</v>
       </c>
-      <c r="C75" s="4">
+      <c r="C75">
         <v>55.931965770821535</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A76" s="4">
+      <c r="A76">
         <v>49</v>
       </c>
-      <c r="B76" s="4">
+      <c r="B76">
         <v>3143.0075859642993</v>
       </c>
-      <c r="C76" s="4">
+      <c r="C76">
         <v>195.99241403570068</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A77" s="4">
+      <c r="A77">
         <v>50</v>
       </c>
-      <c r="B77" s="4">
+      <c r="B77">
         <v>3335.0819785277754</v>
       </c>
-      <c r="C77" s="4">
+      <c r="C77">
         <v>263.91802147222461</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A78" s="4">
+      <c r="A78">
         <v>51</v>
       </c>
-      <c r="B78" s="4">
+      <c r="B78">
         <v>5768.9187562760308</v>
       </c>
-      <c r="C78" s="4">
+      <c r="C78">
         <v>747.08124372396924</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A79" s="4">
+      <c r="A79">
         <v>52</v>
       </c>
-      <c r="B79" s="4">
+      <c r="B79">
         <v>7258.072011200441</v>
       </c>
-      <c r="C79" s="4">
+      <c r="C79">
         <v>-163.07201120044101</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A80" s="4">
+      <c r="A80">
         <v>53</v>
       </c>
-      <c r="B80" s="4">
+      <c r="B80">
         <v>8067.693507161609</v>
       </c>
-      <c r="C80" s="4">
+      <c r="C80">
         <v>535.30649283839102</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A81" s="4">
+      <c r="A81">
         <v>54</v>
       </c>
-      <c r="B81" s="4">
+      <c r="B81">
         <v>6533.7510437063902</v>
       </c>
-      <c r="C81" s="4">
+      <c r="C81">
         <v>551.24895629360981</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A82" s="4">
+      <c r="A82">
         <v>55</v>
       </c>
-      <c r="B82" s="4">
+      <c r="B82">
         <v>5356.5777841630088</v>
       </c>
-      <c r="C82" s="4">
+      <c r="C82">
         <v>-274.5777841630088</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A83" s="4">
+      <c r="A83">
         <v>56</v>
       </c>
-      <c r="B83" s="4">
+      <c r="B83">
         <v>2501.0334076467566</v>
       </c>
-      <c r="C83" s="4">
+      <c r="C83">
         <v>-171.03340764675659</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A84" s="4">
+      <c r="A84">
         <v>57</v>
       </c>
-      <c r="B84" s="4">
+      <c r="B84">
         <v>6278.9064900543608</v>
       </c>
-      <c r="C84" s="4">
+      <c r="C84">
         <v>-558.9064900543608</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A85" s="4">
+      <c r="A85">
         <v>58</v>
       </c>
-      <c r="B85" s="4">
+      <c r="B85">
         <v>3248.2461097761475</v>
       </c>
-      <c r="C85" s="4">
+      <c r="C85">
         <v>-560.24610977614748</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A86" s="4">
+      <c r="A86">
         <v>59</v>
       </c>
-      <c r="B86" s="4">
+      <c r="B86">
         <v>4131.4486597395471</v>
       </c>
-      <c r="C86" s="4">
+      <c r="C86">
         <v>234.55134026045289</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A87" s="4">
+      <c r="A87">
         <v>60</v>
       </c>
-      <c r="B87" s="4">
+      <c r="B87">
         <v>4338.9756368317294</v>
       </c>
-      <c r="C87" s="4">
+      <c r="C87">
         <v>31.024363168270611</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A88" s="4">
+      <c r="A88">
         <v>61</v>
       </c>
-      <c r="B88" s="4">
+      <c r="B88">
         <v>5855.2701817426787</v>
       </c>
-      <c r="C88" s="4">
+      <c r="C88">
         <v>358.72981825732131</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A89" s="4">
+      <c r="A89">
         <v>62</v>
       </c>
-      <c r="B89" s="4">
+      <c r="B89">
         <v>4892.9670736178668</v>
       </c>
-      <c r="C89" s="4">
+      <c r="C89">
         <v>-344.96707361786684</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A90" s="4">
+      <c r="A90">
         <v>63</v>
       </c>
-      <c r="B90" s="4">
+      <c r="B90">
         <v>2751.35934571196</v>
       </c>
-      <c r="C90" s="4">
+      <c r="C90">
         <v>-488.35934571196003</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A91" s="4">
+      <c r="A91">
         <v>64</v>
       </c>
-      <c r="B91" s="4">
+      <c r="B91">
         <v>4317.0105203993171</v>
       </c>
-      <c r="C91" s="4">
+      <c r="C91">
         <v>-476.0105203993171</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A92" s="4">
+      <c r="A92">
         <v>65</v>
       </c>
-      <c r="B92" s="4">
+      <c r="B92">
         <v>3930.7894772850059</v>
       </c>
-      <c r="C92" s="4">
+      <c r="C92">
         <v>336.21052271499411</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A93" s="4">
+      <c r="A93">
         <v>66</v>
       </c>
-      <c r="B93" s="4">
+      <c r="B93">
         <v>8083.1153226832648</v>
       </c>
-      <c r="C93" s="4">
+      <c r="C93">
         <v>-312.11532268326482</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A94" s="4">
+      <c r="A94">
         <v>67</v>
       </c>
-      <c r="B94" s="4">
+      <c r="B94">
         <v>2965.5399673877732</v>
       </c>
-      <c r="C94" s="4">
+      <c r="C94">
         <v>456.46003261222677</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A95" s="4">
+      <c r="A95">
         <v>68</v>
       </c>
-      <c r="B95" s="4">
+      <c r="B95">
         <v>5350.003714245202</v>
       </c>
-      <c r="C95" s="4">
+      <c r="C95">
         <v>163.99628575479801</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A96" s="4">
+      <c r="A96">
         <v>69</v>
       </c>
-      <c r="B96" s="4">
+      <c r="B96">
         <v>4374.7595859643416</v>
       </c>
-      <c r="C96" s="4">
+      <c r="C96">
         <v>32.240414035658432</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A97" s="4">
+      <c r="A97">
         <v>70</v>
       </c>
-      <c r="B97" s="4">
+      <c r="B97">
         <v>7110.3971266676945</v>
       </c>
-      <c r="C97" s="4">
+      <c r="C97">
         <v>-248.39712666769447</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A98" s="4">
+      <c r="A98">
         <v>71</v>
       </c>
-      <c r="B98" s="4">
+      <c r="B98">
         <v>5396.0345383406893</v>
       </c>
-      <c r="C98" s="4">
+      <c r="C98">
         <v>-704.03453834068932</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A99" s="4">
+      <c r="A99">
         <v>72</v>
       </c>
-      <c r="B99" s="4">
+      <c r="B99">
         <v>5300.4908036697925</v>
       </c>
-      <c r="C99" s="4">
+      <c r="C99">
         <v>-342.49080366979251</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A100" s="4">
+      <c r="A100">
         <v>73</v>
       </c>
-      <c r="B100" s="4">
+      <c r="B100">
         <v>4923.418568397351</v>
       </c>
-      <c r="C100" s="4">
+      <c r="C100">
         <v>182.58143160264899</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A101" s="4">
+      <c r="A101">
         <v>74</v>
       </c>
-      <c r="B101" s="4">
+      <c r="B101">
         <v>8687.5306873597638</v>
       </c>
-      <c r="C101" s="4">
+      <c r="C101">
         <v>668.46931264023624</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A102" s="4">
+      <c r="A102">
         <v>75</v>
       </c>
-      <c r="B102" s="4">
+      <c r="B102">
         <v>6807.3571839116676</v>
       </c>
-      <c r="C102" s="4">
+      <c r="C102">
         <v>352.64281608833244</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A103" s="4">
+      <c r="A103">
         <v>76</v>
       </c>
-      <c r="B103" s="4">
+      <c r="B103">
         <v>3967.8946166481214</v>
       </c>
-      <c r="C103" s="4">
+      <c r="C103">
         <v>-345.89461664812143</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A104" s="4">
+      <c r="A104">
         <v>77</v>
       </c>
-      <c r="B104" s="4">
+      <c r="B104">
         <v>5866.9884232122167</v>
       </c>
-      <c r="C104" s="4">
+      <c r="C104">
         <v>1241.0115767877833</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A105" s="4">
+      <c r="A105">
         <v>78</v>
       </c>
-      <c r="B105" s="4">
+      <c r="B105">
         <v>4848.9597018509658</v>
       </c>
-      <c r="C105" s="4">
+      <c r="C105">
         <v>-771.95970185096576</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A106" s="4">
+      <c r="A106">
         <v>79</v>
       </c>
-      <c r="B106" s="4">
+      <c r="B106">
         <v>4450.3001185173107</v>
       </c>
-      <c r="C106" s="4">
+      <c r="C106">
         <v>-55.300118517310693</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A107" s="4">
+      <c r="A107">
         <v>80</v>
       </c>
-      <c r="B107" s="4">
+      <c r="B107">
         <v>5464.7651455110235</v>
       </c>
-      <c r="C107" s="4">
+      <c r="C107">
         <v>-167.76514551102355</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A108" s="4">
+      <c r="A108">
         <v>81</v>
       </c>
-      <c r="B108" s="4">
+      <c r="B108">
         <v>5618.1682894198211</v>
       </c>
-      <c r="C108" s="4">
+      <c r="C108">
         <v>9.8317105801788784</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A109" s="4">
+      <c r="A109">
         <v>82</v>
       </c>
-      <c r="B109" s="4">
+      <c r="B109">
         <v>5629.4328566114291</v>
       </c>
-      <c r="C109" s="4">
+      <c r="C109">
         <v>-14.432856611429088</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A110" s="4">
+      <c r="A110">
         <v>83</v>
       </c>
-      <c r="B110" s="4">
+      <c r="B110">
         <v>5744.0380070782503</v>
       </c>
-      <c r="C110" s="4">
+      <c r="C110">
         <v>-620.0380070782503</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A111" s="4">
+      <c r="A111">
         <v>84</v>
       </c>
-      <c r="B111" s="4">
+      <c r="B111">
         <v>3641.9973770228985</v>
       </c>
-      <c r="C111" s="4">
+      <c r="C111">
         <v>12.00262297710151</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A112" s="4">
+      <c r="A112">
         <v>85</v>
       </c>
-      <c r="B112" s="4">
+      <c r="B112">
         <v>5771.4446885413199</v>
       </c>
-      <c r="C112" s="4">
+      <c r="C112">
         <v>31.55531145868008</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A113" s="4">
+      <c r="A113">
         <v>86</v>
       </c>
-      <c r="B113" s="4">
+      <c r="B113">
         <v>5879.3014516396097</v>
       </c>
-      <c r="C113" s="4">
+      <c r="C113">
         <v>517.6985483603903</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A114" s="4">
+      <c r="A114">
         <v>87</v>
       </c>
-      <c r="B114" s="4">
+      <c r="B114">
         <v>5647.7395358914046</v>
       </c>
-      <c r="C114" s="4">
+      <c r="C114">
         <v>-80.739535891404557</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A115" s="4">
+      <c r="A115">
         <v>88</v>
       </c>
-      <c r="B115" s="4">
+      <c r="B115">
         <v>8354.8235223519059</v>
       </c>
-      <c r="C115" s="4">
+      <c r="C115">
         <v>-171.82352235190592</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A116" s="4">
+      <c r="A116">
         <v>89</v>
       </c>
-      <c r="B116" s="4">
+      <c r="B116">
         <v>4802.3353237929687</v>
       </c>
-      <c r="C116" s="4">
+      <c r="C116">
         <v>-37.335323792968666</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A117" s="4">
+      <c r="A117">
         <v>90</v>
       </c>
-      <c r="B117" s="4">
+      <c r="B117">
         <v>4025.3914256338994</v>
       </c>
-      <c r="C117" s="4">
+      <c r="C117">
         <v>305.60857436610058</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A118" s="4">
+      <c r="A118">
         <v>91</v>
       </c>
-      <c r="B118" s="4">
+      <c r="B118">
         <v>3700.4052033236276</v>
       </c>
-      <c r="C118" s="4">
+      <c r="C118">
         <v>-241.40520332362757</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A119" s="4">
+      <c r="A119">
         <v>92</v>
       </c>
-      <c r="B119" s="4">
+      <c r="B119">
         <v>3369.565209845357</v>
       </c>
-      <c r="C119" s="4">
+      <c r="C119">
         <v>52.434790154642997</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A120" s="4">
+      <c r="A120">
         <v>93</v>
       </c>
-      <c r="B120" s="4">
+      <c r="B120">
         <v>5341.0636616202</v>
       </c>
-      <c r="C120" s="4">
+      <c r="C120">
         <v>13.936338379799963</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A121" s="4">
+      <c r="A121">
         <v>94</v>
       </c>
-      <c r="B121" s="4">
+      <c r="B121">
         <v>3025.6894534261369</v>
       </c>
-      <c r="C121" s="4">
+      <c r="C121">
         <v>-439.68945342613688</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A122" s="4">
+      <c r="A122">
         <v>95</v>
       </c>
-      <c r="B122" s="4">
+      <c r="B122">
         <v>4186.4503054670859</v>
       </c>
-      <c r="C122" s="4">
+      <c r="C122">
         <v>225.54969453291415</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A123" s="4">
+      <c r="A123">
         <v>96</v>
       </c>
-      <c r="B123" s="4">
+      <c r="B123">
         <v>4185.9621934230136</v>
       </c>
-      <c r="C123" s="4">
+      <c r="C123">
         <v>-220.96219342301356</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A124" s="4">
+      <c r="A124">
         <v>97</v>
       </c>
-      <c r="B124" s="4">
+      <c r="B124">
         <v>6294.6256990549446</v>
       </c>
-      <c r="C124" s="4">
+      <c r="C124">
         <v>219.37430094505544</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A125" s="4">
+      <c r="A125">
         <v>98</v>
       </c>
-      <c r="B125" s="4">
+      <c r="B125">
         <v>5407.1735937403455</v>
       </c>
-      <c r="C125" s="4">
+      <c r="C125">
         <v>70.826406259654505</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A126" s="4">
+      <c r="A126">
         <v>99</v>
       </c>
-      <c r="B126" s="4">
+      <c r="B126">
         <v>3072.2830624770845</v>
       </c>
-      <c r="C126" s="4">
+      <c r="C126">
         <v>543.71693752291549</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A127" s="4">
+      <c r="A127">
         <v>100</v>
       </c>
-      <c r="B127" s="4">
+      <c r="B127">
         <v>5771.3499457564203</v>
       </c>
-      <c r="C127" s="4">
+      <c r="C127">
         <v>-251.34994575642031</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A128" s="4">
+      <c r="A128">
         <v>101</v>
       </c>
-      <c r="B128" s="4">
+      <c r="B128">
         <v>4016.4513730088979</v>
       </c>
-      <c r="C128" s="4">
+      <c r="C128">
         <v>339.54862699110208</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A129" s="4">
+      <c r="A129">
         <v>102</v>
       </c>
-      <c r="B129" s="4">
+      <c r="B129">
         <v>2750.9056714340304</v>
       </c>
-      <c r="C129" s="4">
+      <c r="C129">
         <v>418.09432856596959</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A130" s="4">
+      <c r="A130">
         <v>103</v>
       </c>
-      <c r="B130" s="4">
+      <c r="B130">
         <v>3309.809093066166</v>
       </c>
-      <c r="C130" s="4">
+      <c r="C130">
         <v>64.190906933833958</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A131" s="4">
+      <c r="A131">
         <v>104</v>
       </c>
-      <c r="B131" s="4">
+      <c r="B131">
         <v>4921.5821658748173</v>
       </c>
-      <c r="C131" s="4">
+      <c r="C131">
         <v>-309.58216587481729</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A132" s="4">
+      <c r="A132">
         <v>105</v>
       </c>
-      <c r="B132" s="4">
+      <c r="B132">
         <v>7677.9124384388524</v>
       </c>
-      <c r="C132" s="4">
+      <c r="C132">
         <v>324.0875615611476</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A133" s="4">
+      <c r="A133">
         <v>106</v>
       </c>
-      <c r="B133" s="4">
+      <c r="B133">
         <v>2967.4071389173582</v>
       </c>
-      <c r="C133" s="4">
+      <c r="C133">
         <v>-39.407138917358225</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A134" s="4">
+      <c r="A134">
         <v>107</v>
       </c>
-      <c r="B134" s="4">
+      <c r="B134">
         <v>3290.2903342332188</v>
       </c>
-      <c r="C134" s="4">
+      <c r="C134">
         <v>-247.2903342332188</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A135" s="4">
+      <c r="A135">
         <v>108</v>
       </c>
-      <c r="B135" s="4">
+      <c r="B135">
         <v>2730.6973828583273</v>
       </c>
-      <c r="C135" s="4">
+      <c r="C135">
         <v>186.30261714167273</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A136" s="4">
+      <c r="A136">
         <v>109</v>
       </c>
-      <c r="B136" s="4">
+      <c r="B136">
         <v>4145.3622352246484</v>
       </c>
-      <c r="C136" s="4">
+      <c r="C136">
         <v>644.63776477535157</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A137" s="4">
+      <c r="A137">
         <v>110</v>
       </c>
-      <c r="B137" s="4">
+      <c r="B137">
         <v>5327.0516745911063</v>
       </c>
-      <c r="C137" s="4">
+      <c r="C137">
         <v>3.9483254088936519</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A138" s="4">
+      <c r="A138">
         <v>111</v>
       </c>
-      <c r="B138" s="4">
+      <c r="B138">
         <v>5673.6416460770124</v>
       </c>
-      <c r="C138" s="4">
+      <c r="C138">
         <v>-404.64164607701241</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A139" s="4">
+      <c r="A139">
         <v>112</v>
       </c>
-      <c r="B139" s="4">
+      <c r="B139">
         <v>3867.5951779302291</v>
       </c>
-      <c r="C139" s="4">
+      <c r="C139">
         <v>262.40482206977094</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A140" s="4">
+      <c r="A140">
         <v>113</v>
       </c>
-      <c r="B140" s="4">
+      <c r="B140">
         <v>6053.0383959160599</v>
       </c>
-      <c r="C140" s="4">
+      <c r="C140">
         <v>-254.03839591605993</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A141" s="4">
+      <c r="A141">
         <v>114</v>
       </c>
-      <c r="B141" s="4">
+      <c r="B141">
         <v>4293.5252318014673</v>
       </c>
-      <c r="C141" s="4">
+      <c r="C141">
         <v>596.47476819853273</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A142" s="4">
+      <c r="A142">
         <v>115</v>
       </c>
-      <c r="B142" s="4">
+      <c r="B142">
         <v>5262.1501532648399</v>
       </c>
-      <c r="C142" s="4">
+      <c r="C142">
         <v>-436.1501532648399</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A143" s="4">
+      <c r="A143">
         <v>116</v>
       </c>
-      <c r="B143" s="4">
+      <c r="B143">
         <v>8424.0422415663161</v>
       </c>
-      <c r="C143" s="4">
+      <c r="C143">
         <v>-402.04224156631608</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A144" s="4">
+      <c r="A144">
         <v>117</v>
       </c>
-      <c r="B144" s="4">
+      <c r="B144">
         <v>4316.0199284185419</v>
       </c>
-      <c r="C144" s="4">
+      <c r="C144">
         <v>-676.01992841854189</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A145" s="4">
+      <c r="A145">
         <v>118</v>
       </c>
-      <c r="B145" s="4">
+      <c r="B145">
         <v>3454.5646760744507</v>
       </c>
-      <c r="C145" s="4">
+      <c r="C145">
         <v>534.43532392554926</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A146" s="4">
+      <c r="A146">
         <v>119</v>
       </c>
-      <c r="B146" s="4">
+      <c r="B146">
         <v>3544.022452871613</v>
       </c>
-      <c r="C146" s="4">
+      <c r="C146">
         <v>-679.02245287161304</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A147" s="4">
+      <c r="A147">
         <v>120</v>
       </c>
-      <c r="B147" s="4">
+      <c r="B147">
         <v>8040.7097309694163</v>
       </c>
-      <c r="C147" s="4">
+      <c r="C147">
         <v>578.29026903058366</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A148" s="4">
+      <c r="A148">
         <v>121</v>
       </c>
-      <c r="B148" s="4">
+      <c r="B148">
         <v>2796.4791524924949</v>
       </c>
-      <c r="C148" s="4">
+      <c r="C148">
         <v>547.5208475075051</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A149" s="4">
+      <c r="A149">
         <v>122</v>
       </c>
-      <c r="B149" s="4">
+      <c r="B149">
         <v>7142.3544257199874</v>
       </c>
-      <c r="C149" s="4">
+      <c r="C149">
         <v>1573.6455742800126</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A150" s="4">
+      <c r="A150">
         <v>123</v>
       </c>
-      <c r="B150" s="4">
+      <c r="B150">
         <v>4973.1185287788121</v>
       </c>
-      <c r="C150" s="4">
+      <c r="C150">
         <v>-263.11852877881211</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A151" s="4">
+      <c r="A151">
         <v>124</v>
       </c>
-      <c r="B151" s="4">
+      <c r="B151">
         <v>3865.0077076508383</v>
       </c>
-      <c r="C151" s="4">
+      <c r="C151">
         <v>-21.007707650838256</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A152" s="4">
+      <c r="A152">
         <v>125</v>
       </c>
-      <c r="B152" s="4">
+      <c r="B152">
         <v>6437.5485482997892</v>
       </c>
-      <c r="C152" s="4">
+      <c r="C152">
         <v>-268.54854829978922</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A153" s="4">
+      <c r="A153">
         <v>126</v>
       </c>
-      <c r="B153" s="4">
+      <c r="B153">
         <v>6058.5747037316187</v>
       </c>
-      <c r="C153" s="4">
+      <c r="C153">
         <v>409.42529626838132</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A154" s="4">
+      <c r="A154">
         <v>127</v>
       </c>
-      <c r="B154" s="4">
+      <c r="B154">
         <v>8435.306808757925</v>
       </c>
-      <c r="C154" s="4">
+      <c r="C154">
         <v>-1077.306808757925</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A155" s="4">
+      <c r="A155">
         <v>128</v>
       </c>
-      <c r="B155" s="4">
+      <c r="B155">
         <v>4282.7939135536135</v>
       </c>
-      <c r="C155" s="4">
+      <c r="C155">
         <v>385.20608644638651</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A156" s="4">
+      <c r="A156">
         <v>129</v>
       </c>
-      <c r="B156" s="4">
+      <c r="B156">
         <v>5190.3095260048967</v>
       </c>
-      <c r="C156" s="4">
+      <c r="C156">
         <v>404.69047399510328</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A157" s="4">
+      <c r="A157">
         <v>130</v>
       </c>
-      <c r="B157" s="4">
+      <c r="B157">
         <v>4230.1746516476896</v>
       </c>
-      <c r="C157" s="4">
+      <c r="C157">
         <v>-884.17465164768964</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A158" s="4">
+      <c r="A158">
         <v>131</v>
       </c>
-      <c r="B158" s="4">
+      <c r="B158">
         <v>3434.6266807297175</v>
       </c>
-      <c r="C158" s="4">
+      <c r="C158">
         <v>437.37331927028254</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A159" s="4">
+      <c r="A159">
         <v>132</v>
       </c>
-      <c r="B159" s="4">
+      <c r="B159">
         <v>3061.3195575234963</v>
       </c>
-      <c r="C159" s="4">
+      <c r="C159">
         <v>-164.31955752349631</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A160" s="4">
+      <c r="A160">
         <v>133</v>
       </c>
-      <c r="B160" s="4">
+      <c r="B160">
         <v>3421.5257110155749</v>
       </c>
-      <c r="C160" s="4">
+      <c r="C160">
         <v>-66.525711015574871</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A161" s="4">
+      <c r="A161">
         <v>134</v>
       </c>
-      <c r="B161" s="4">
+      <c r="B161">
         <v>4410.4204590687523</v>
       </c>
-      <c r="C161" s="4">
+      <c r="C161">
         <v>558.57954093124772</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A162" s="4">
+      <c r="A162">
         <v>135</v>
       </c>
-      <c r="B162" s="4">
+      <c r="B162">
         <v>3870.3425977677148</v>
       </c>
-      <c r="C162" s="4">
+      <c r="C162">
         <v>-138.34259776771478</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A163" s="4">
+      <c r="A163">
         <v>136</v>
       </c>
-      <c r="B163" s="4">
+      <c r="B163">
         <v>5036.5486835984157</v>
       </c>
-      <c r="C163" s="4">
+      <c r="C163">
         <v>885.45131640158434</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A164" s="4">
+      <c r="A164">
         <v>137</v>
       </c>
-      <c r="B164" s="4">
+      <c r="B164">
         <v>2749.0692689114967</v>
       </c>
-      <c r="C164" s="4">
+      <c r="C164">
         <v>239.93073108850331</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A165" s="4">
+      <c r="A165">
         <v>138</v>
       </c>
-      <c r="B165" s="4">
+      <c r="B165">
         <v>3845.3055677709322</v>
       </c>
-      <c r="C165" s="4">
+      <c r="C165">
         <v>639.69443222906784</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A166" s="4">
+      <c r="A166">
         <v>139</v>
       </c>
-      <c r="B166" s="4">
+      <c r="B166">
         <v>3717.6941903748684</v>
       </c>
-      <c r="C166" s="4">
+      <c r="C166">
         <v>550.30580962513159</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A167" s="4">
+      <c r="A167">
         <v>140</v>
       </c>
-      <c r="B167" s="4">
+      <c r="B167">
         <v>4162.0232305472337</v>
       </c>
-      <c r="C167" s="4">
+      <c r="C167">
         <v>-974.02323054723365</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A168" s="4">
+      <c r="A168">
         <v>141</v>
       </c>
-      <c r="B168" s="4">
+      <c r="B168">
         <v>5474.429165644925</v>
       </c>
-      <c r="C168" s="4">
+      <c r="C168">
         <v>362.57083435507502</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A169" s="4">
+      <c r="A169">
         <v>142</v>
       </c>
-      <c r="B169" s="4">
+      <c r="B169">
         <v>4452.5901953177736</v>
       </c>
-      <c r="C169" s="4">
+      <c r="C169">
         <v>-308.59019531777358</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A170" s="4">
+      <c r="A170">
         <v>143</v>
       </c>
-      <c r="B170" s="4">
+      <c r="B170">
         <v>2608.1391029881884</v>
       </c>
-      <c r="C170" s="4">
+      <c r="C170">
         <v>658.86089701181163</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A171" s="4">
+      <c r="A171">
         <v>144</v>
       </c>
-      <c r="B171" s="4">
+      <c r="B171">
         <v>3672.964084094413</v>
       </c>
-      <c r="C171" s="4">
+      <c r="C171">
         <v>119.03591590558699</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A172" s="4">
+      <c r="A172">
         <v>145</v>
       </c>
-      <c r="B172" s="4">
+      <c r="B172">
         <v>4302.8610894493895</v>
       </c>
-      <c r="C172" s="4">
+      <c r="C172">
         <v>53.13891055061049</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A173" s="4">
+      <c r="A173">
         <v>146</v>
       </c>
-      <c r="B173" s="4">
+      <c r="B173">
         <v>5664.7015934520105</v>
       </c>
-      <c r="C173" s="4">
+      <c r="C173">
         <v>-505.70159345201046</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A174" s="4">
+      <c r="A174">
         <v>147</v>
       </c>
-      <c r="B174" s="4">
+      <c r="B174">
         <v>3277.7902559997729</v>
       </c>
-      <c r="C174" s="4">
+      <c r="C174">
         <v>-32.790255999772853</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A175" s="4">
+      <c r="A175">
         <v>148</v>
       </c>
-      <c r="B175" s="4">
+      <c r="B175">
         <v>6792.5941291257159</v>
       </c>
-      <c r="C175" s="4">
+      <c r="C175">
         <v>-98.594129125715881</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A176" s="4">
+      <c r="A176">
         <v>149</v>
       </c>
-      <c r="B176" s="4">
+      <c r="B176">
         <v>3927.7483327276855</v>
       </c>
-      <c r="C176" s="4">
+      <c r="C176">
         <v>152.25166727231453</v>
       </c>
     </row>
     <row r="177" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A177" s="5">
+      <c r="A177" s="4">
         <v>150</v>
       </c>
-      <c r="B177" s="5">
+      <c r="B177" s="4">
         <v>3434.2037754588387</v>
       </c>
-      <c r="C177" s="5">
+      <c r="C177" s="4">
         <v>-435.20377545883866</v>
       </c>
     </row>
@@ -22181,7 +24273,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E424753-1B2A-4666-BD52-BCA9720CB876}">
   <dimension ref="A1:C14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -22198,299 +24290,111 @@
     </row>
     <row r="2" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="6"/>
-      <c r="B3" s="6" t="s">
+      <c r="A3" s="5"/>
+      <c r="B3" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="5" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
+      <c r="A4" t="s">
         <v>81</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4">
         <v>74.680000000000007</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4">
         <v>69.213333333333338</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
+      <c r="A5" t="s">
         <v>117</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5">
         <v>96.876778523490032</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5">
         <v>89.913914988814355</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="4" t="s">
+      <c r="A6" t="s">
         <v>94</v>
       </c>
-      <c r="B6" s="4">
+      <c r="B6">
         <v>150</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6">
         <v>150</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="4" t="s">
+      <c r="A7" t="s">
         <v>118</v>
       </c>
-      <c r="B7" s="4">
+      <c r="B7">
         <v>0.95937109676348009</v>
       </c>
-      <c r="C7" s="4"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="4" t="s">
+      <c r="A8" t="s">
         <v>119</v>
       </c>
-      <c r="B8" s="4">
+      <c r="B8">
         <v>0</v>
       </c>
-      <c r="C8" s="4"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="4" t="s">
+      <c r="A9" t="s">
         <v>100</v>
       </c>
-      <c r="B9" s="4">
+      <c r="B9">
         <v>149</v>
       </c>
-      <c r="C9" s="4"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="4" t="s">
+      <c r="A10" t="s">
         <v>106</v>
       </c>
-      <c r="B10" s="4">
+      <c r="B10">
         <v>24.106732892817753</v>
       </c>
-      <c r="C10" s="4"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="4" t="s">
+      <c r="A11" t="s">
         <v>120</v>
       </c>
-      <c r="B11" s="4">
+      <c r="B11">
         <v>1.3844492251729054E-53</v>
       </c>
-      <c r="C11" s="4"/>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" s="4" t="s">
+      <c r="A12" t="s">
         <v>121</v>
       </c>
-      <c r="B12" s="4">
+      <c r="B12">
         <v>1.6551445337979596</v>
       </c>
-      <c r="C12" s="4"/>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" s="4" t="s">
+      <c r="A13" t="s">
         <v>122</v>
       </c>
-      <c r="B13" s="4">
+      <c r="B13">
         <v>2.7688984503458108E-53</v>
       </c>
-      <c r="C13" s="4"/>
     </row>
     <row r="14" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="B14" s="5">
+      <c r="B14" s="4">
         <v>1.976013177689196</v>
       </c>
-      <c r="C14" s="5"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCF05E2F-7C27-4080-931D-688323CA3A9C}">
-  <dimension ref="A3:D22"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="18.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.88671875" customWidth="1"/>
-    <col min="3" max="3" width="4.21875" customWidth="1"/>
-    <col min="4" max="4" width="10.77734375" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="9" t="s">
-        <v>137</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="B4">
-        <v>0</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="11">
-        <v>49</v>
-      </c>
-      <c r="C5" s="11">
-        <v>24</v>
-      </c>
-      <c r="D5" s="11">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" s="11">
-        <v>32</v>
-      </c>
-      <c r="C6" s="11">
-        <v>45</v>
-      </c>
-      <c r="D6" s="11">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="10" t="s">
-        <v>135</v>
-      </c>
-      <c r="B7" s="11">
-        <v>81</v>
-      </c>
-      <c r="C7" s="11">
-        <v>69</v>
-      </c>
-      <c r="D7" s="11">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="10"/>
-      <c r="B9" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10">
-        <f>GETPIVOTDATA("[Measures].[Count of Conversion]",$A$3,"[Range].[Website_Group]","[Range].[Website_Group].&amp;[A]","[Range].[Conversion]","[Range].[Conversion].&amp;[1]")/GETPIVOTDATA("[Measures].[Count of Conversion]",$A$3,"[Range].[Website_Group]","[Range].[Website_Group].&amp;[A]")</f>
-        <v>0.32876712328767121</v>
-      </c>
-      <c r="C10">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11">
-        <f>GETPIVOTDATA("[Measures].[Count of Conversion]",$A$3,"[Range].[Website_Group]","[Range].[Website_Group].&amp;[B]","[Range].[Conversion]","[Range].[Conversion].&amp;[1]")/GETPIVOTDATA("[Measures].[Count of Conversion]",$A$3,"[Range].[Website_Group]","[Range].[Website_Group].&amp;[B]")</f>
-        <v>0.58441558441558439</v>
-      </c>
-      <c r="C11">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="10" t="s">
-        <v>140</v>
-      </c>
-      <c r="C12">
-        <f>C11-C10</f>
-        <v>25</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="10" t="s">
-        <v>141</v>
-      </c>
-      <c r="B14">
-        <v>0</v>
-      </c>
-      <c r="C14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="B15">
-        <f>GETPIVOTDATA("[Measures].[Count of Conversion]",$A$3,"[Range].[Website_Group]","[Range].[Website_Group].&amp;[A]")*GETPIVOTDATA("[Measures].[Count of Conversion]",$A$3,"[Range].[Conversion]","[Range].[Conversion].&amp;[0]")/GETPIVOTDATA("[Measures].[Count of Conversion]",$A$3)</f>
-        <v>39.42</v>
-      </c>
-      <c r="C15">
-        <f>GETPIVOTDATA("[Measures].[Count of Conversion]",$A$3,"[Range].[Website_Group]","[Range].[Website_Group].&amp;[A]")*GETPIVOTDATA("[Measures].[Count of Conversion]",$A$3,"[Range].[Conversion]","[Range].[Conversion].&amp;[1]")/GETPIVOTDATA("[Measures].[Count of Conversion]",$A$3)</f>
-        <v>33.58</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="B16">
-        <f>GETPIVOTDATA("[Measures].[Count of Conversion]",$A$3,"[Range].[Website_Group]","[Range].[Website_Group].&amp;[B]")*GETPIVOTDATA("[Measures].[Count of Conversion]",$A$3,"[Range].[Conversion]","[Range].[Conversion].&amp;[0]")/GETPIVOTDATA("[Measures].[Count of Conversion]",$A$3)</f>
-        <v>41.58</v>
-      </c>
-      <c r="C16">
-        <f>GETPIVOTDATA("[Measures].[Count of Conversion]",$A$3,"[Range].[Website_Group]","[Range].[Website_Group].&amp;[B]")*GETPIVOTDATA("[Measures].[Count of Conversion]",$A$3,"[Range].[Conversion]","[Range].[Conversion].&amp;[1]")/GETPIVOTDATA("[Measures].[Count of Conversion]",$A$3)</f>
-        <v>35.42</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>142</v>
-      </c>
-      <c r="B18">
-        <f>_xlfn.CHISQ.TEST(B5:C6, B10:C11)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19" s="10"/>
-      <c r="B19" s="11"/>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20" s="10"/>
-      <c r="B20" s="11"/>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21" s="10"/>
-      <c r="B21" s="11"/>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22" s="10"/>
-      <c r="B22" s="11"/>
+      <c r="C14" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -22498,6 +24402,183 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCF05E2F-7C27-4080-931D-688323CA3A9C}">
+  <dimension ref="A3:D22"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.77734375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="14">
+        <v>49</v>
+      </c>
+      <c r="C5" s="14">
+        <v>24</v>
+      </c>
+      <c r="D5" s="14">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="14">
+        <v>32</v>
+      </c>
+      <c r="C6" s="14">
+        <v>45</v>
+      </c>
+      <c r="D6" s="14">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="B7" s="14">
+        <v>81</v>
+      </c>
+      <c r="C7" s="14">
+        <v>69</v>
+      </c>
+      <c r="D7" s="14">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="8"/>
+      <c r="B9" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10">
+        <f>GETPIVOTDATA("[Measures].[Count of Conversion]",$A$3,"[Range].[Website_Group]","[Range].[Website_Group].&amp;[A]","[Range].[Conversion]","[Range].[Conversion].&amp;[1]")/GETPIVOTDATA("[Measures].[Count of Conversion]",$A$3,"[Range].[Website_Group]","[Range].[Website_Group].&amp;[A]")</f>
+        <v>0.32876712328767121</v>
+      </c>
+      <c r="C10">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11">
+        <f>GETPIVOTDATA("[Measures].[Count of Conversion]",$A$3,"[Range].[Website_Group]","[Range].[Website_Group].&amp;[B]","[Range].[Conversion]","[Range].[Conversion].&amp;[1]")/GETPIVOTDATA("[Measures].[Count of Conversion]",$A$3,"[Range].[Website_Group]","[Range].[Website_Group].&amp;[B]")</f>
+        <v>0.58441558441558439</v>
+      </c>
+      <c r="C11">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="C12">
+        <f>C11-C10</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="B14">
+        <v>0</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15">
+        <f>GETPIVOTDATA("[Measures].[Count of Conversion]",$A$3,"[Range].[Website_Group]","[Range].[Website_Group].&amp;[A]")*GETPIVOTDATA("[Measures].[Count of Conversion]",$A$3,"[Range].[Conversion]","[Range].[Conversion].&amp;[0]")/GETPIVOTDATA("[Measures].[Count of Conversion]",$A$3)</f>
+        <v>39.42</v>
+      </c>
+      <c r="C15">
+        <f>GETPIVOTDATA("[Measures].[Count of Conversion]",$A$3,"[Range].[Website_Group]","[Range].[Website_Group].&amp;[A]")*GETPIVOTDATA("[Measures].[Count of Conversion]",$A$3,"[Range].[Conversion]","[Range].[Conversion].&amp;[1]")/GETPIVOTDATA("[Measures].[Count of Conversion]",$A$3)</f>
+        <v>33.58</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16">
+        <f>GETPIVOTDATA("[Measures].[Count of Conversion]",$A$3,"[Range].[Website_Group]","[Range].[Website_Group].&amp;[B]")*GETPIVOTDATA("[Measures].[Count of Conversion]",$A$3,"[Range].[Conversion]","[Range].[Conversion].&amp;[0]")/GETPIVOTDATA("[Measures].[Count of Conversion]",$A$3)</f>
+        <v>41.58</v>
+      </c>
+      <c r="C16">
+        <f>GETPIVOTDATA("[Measures].[Count of Conversion]",$A$3,"[Range].[Website_Group]","[Range].[Website_Group].&amp;[B]")*GETPIVOTDATA("[Measures].[Count of Conversion]",$A$3,"[Range].[Conversion]","[Range].[Conversion].&amp;[1]")/GETPIVOTDATA("[Measures].[Count of Conversion]",$A$3)</f>
+        <v>35.42</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>142</v>
+      </c>
+      <c r="B18">
+        <f>_xlfn.CHISQ.TEST(B5:C6, B10:C11)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" s="8"/>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" s="8"/>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" s="8"/>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" s="8"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{916A6440-3289-4DAD-BD79-7F8DC834BF4A}">
   <dimension ref="A1:Q152"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -22595,19 +24676,19 @@
       <c r="F5">
         <v>82</v>
       </c>
-      <c r="K5" s="6" t="s">
+      <c r="K5" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="L5" s="6" t="s">
+      <c r="L5" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="M5" s="6" t="s">
+      <c r="M5" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="N5" s="6" t="s">
+      <c r="N5" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="O5" s="6" t="s">
+      <c r="O5" s="5" t="s">
         <v>117</v>
       </c>
     </row>
@@ -22627,19 +24708,19 @@
       <c r="F6">
         <v>80</v>
       </c>
-      <c r="K6" s="4" t="s">
+      <c r="K6" t="s">
         <v>12</v>
       </c>
-      <c r="L6" s="4">
+      <c r="L6">
         <v>53</v>
       </c>
-      <c r="M6" s="4">
+      <c r="M6">
         <v>3846</v>
       </c>
-      <c r="N6" s="4">
+      <c r="N6">
         <v>72.566037735849051</v>
       </c>
-      <c r="O6" s="4">
+      <c r="O6">
         <v>89.750362844702281</v>
       </c>
     </row>
@@ -22659,19 +24740,19 @@
       <c r="F7">
         <v>72</v>
       </c>
-      <c r="K7" s="4" t="s">
+      <c r="K7" t="s">
         <v>15</v>
       </c>
-      <c r="L7" s="4">
+      <c r="L7">
         <v>50</v>
       </c>
-      <c r="M7" s="4">
+      <c r="M7">
         <v>3623</v>
       </c>
-      <c r="N7" s="4">
+      <c r="N7">
         <v>72.459999999999994</v>
       </c>
-      <c r="O7" s="4">
+      <c r="O7">
         <v>77.559591836734356</v>
       </c>
     </row>
@@ -22691,19 +24772,19 @@
       <c r="F8">
         <v>79</v>
       </c>
-      <c r="K8" s="5" t="s">
+      <c r="K8" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="L8" s="5">
+      <c r="L8" s="4">
         <v>47</v>
       </c>
-      <c r="M8" s="5">
+      <c r="M8" s="4">
         <v>3349</v>
       </c>
-      <c r="N8" s="5">
+      <c r="N8" s="4">
         <v>71.255319148936167</v>
       </c>
-      <c r="O8" s="5">
+      <c r="O8" s="4">
         <v>106.49861239592998</v>
       </c>
     </row>
@@ -22777,25 +24858,25 @@
       <c r="F12">
         <v>56</v>
       </c>
-      <c r="K12" s="6" t="s">
+      <c r="K12" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="L12" s="6" t="s">
+      <c r="L12" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="M12" s="6" t="s">
+      <c r="M12" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="N12" s="6" t="s">
+      <c r="N12" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="O12" s="6" t="s">
+      <c r="O12" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="P12" s="6" t="s">
+      <c r="P12" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="Q12" s="6" t="s">
+      <c r="Q12" s="5" t="s">
         <v>131</v>
       </c>
     </row>
@@ -22815,25 +24896,25 @@
       <c r="F13">
         <v>80</v>
       </c>
-      <c r="K13" s="4" t="s">
+      <c r="K13" t="s">
         <v>132</v>
       </c>
-      <c r="L13" s="4">
+      <c r="L13">
         <v>51.46496186269178</v>
       </c>
-      <c r="M13" s="4">
+      <c r="M13">
         <v>2</v>
       </c>
-      <c r="N13" s="4">
+      <c r="N13">
         <v>25.73248093134589</v>
       </c>
-      <c r="O13" s="4">
+      <c r="O13">
         <v>0.28299929383359501</v>
       </c>
-      <c r="P13" s="4">
+      <c r="P13">
         <v>0.753929913743276</v>
       </c>
-      <c r="Q13" s="4">
+      <c r="Q13">
         <v>3.0576206516493913</v>
       </c>
     </row>
@@ -22853,21 +24934,18 @@
       <c r="F14">
         <v>82</v>
       </c>
-      <c r="K14" s="4" t="s">
+      <c r="K14" t="s">
         <v>133</v>
       </c>
-      <c r="L14" s="4">
+      <c r="L14">
         <v>13366.375038137294</v>
       </c>
-      <c r="M14" s="4">
+      <c r="M14">
         <v>147</v>
       </c>
-      <c r="N14" s="4">
+      <c r="N14">
         <v>90.927721347872748</v>
       </c>
-      <c r="O14" s="4"/>
-      <c r="P14" s="4"/>
-      <c r="Q14" s="4"/>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
@@ -22885,13 +24963,6 @@
       <c r="F15">
         <v>62</v>
       </c>
-      <c r="K15" s="4"/>
-      <c r="L15" s="4"/>
-      <c r="M15" s="4"/>
-      <c r="N15" s="4"/>
-      <c r="O15" s="4"/>
-      <c r="P15" s="4"/>
-      <c r="Q15" s="4"/>
     </row>
     <row r="16" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
@@ -22909,19 +24980,19 @@
       <c r="F16">
         <v>88</v>
       </c>
-      <c r="K16" s="5" t="s">
+      <c r="K16" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="L16" s="5">
+      <c r="L16" s="4">
         <v>13417.839999999986</v>
       </c>
-      <c r="M16" s="5">
+      <c r="M16" s="4">
         <v>149</v>
       </c>
-      <c r="N16" s="5"/>
-      <c r="O16" s="5"/>
-      <c r="P16" s="5"/>
-      <c r="Q16" s="5"/>
+      <c r="N16" s="4"/>
+      <c r="O16" s="4"/>
+      <c r="P16" s="4"/>
+      <c r="Q16" s="4"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
@@ -24331,7 +26402,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6850A36E-0706-49FD-9094-30E99BFD670A}">
   <dimension ref="A17:G84"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -24341,8 +26412,8 @@
     <col min="3" max="3" width="16.33203125" customWidth="1"/>
     <col min="4" max="4" width="15" customWidth="1"/>
     <col min="5" max="5" width="18.6640625" customWidth="1"/>
-    <col min="6" max="6" width="13.21875" customWidth="1"/>
-    <col min="7" max="7" width="19.77734375" customWidth="1"/>
+    <col min="6" max="6" width="18.21875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="17" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
@@ -24518,136 +26589,121 @@
     </row>
     <row r="48" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A49" s="6"/>
-      <c r="B49" s="6" t="s">
+      <c r="A49" s="5"/>
+      <c r="B49" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C49" s="6" t="s">
+      <c r="C49" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D49" s="6" t="s">
+      <c r="D49" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E49" s="6" t="s">
+      <c r="E49" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F49" s="6" t="s">
+      <c r="F49" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="G49" s="6" t="s">
+      <c r="G49" s="5" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A50" s="4" t="s">
+      <c r="A50" t="s">
         <v>1</v>
       </c>
-      <c r="B50" s="4">
+      <c r="B50">
         <v>1</v>
       </c>
-      <c r="C50" s="4"/>
-      <c r="D50" s="4"/>
-      <c r="E50" s="4"/>
-      <c r="F50" s="4"/>
-      <c r="G50" s="4"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A51" s="4" t="s">
+      <c r="A51" t="s">
         <v>2</v>
       </c>
-      <c r="B51" s="4">
+      <c r="B51">
         <v>0.63227416007095127</v>
       </c>
-      <c r="C51" s="4">
+      <c r="C51">
         <v>1</v>
       </c>
-      <c r="D51" s="4"/>
-      <c r="E51" s="4"/>
-      <c r="F51" s="4"/>
-      <c r="G51" s="4"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A52" s="4" t="s">
+      <c r="A52" t="s">
         <v>3</v>
       </c>
-      <c r="B52" s="4">
+      <c r="B52">
         <v>-3.5597700953125942E-2</v>
       </c>
-      <c r="C52" s="4">
+      <c r="C52">
         <v>-3.0905328079871095E-3</v>
       </c>
-      <c r="D52" s="4">
+      <c r="D52">
         <v>1</v>
       </c>
-      <c r="E52" s="4"/>
-      <c r="F52" s="4"/>
-      <c r="G52" s="4"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A53" s="4" t="s">
+      <c r="A53" t="s">
         <v>4</v>
       </c>
-      <c r="B53" s="4">
+      <c r="B53">
         <v>-0.1350653139096577</v>
       </c>
-      <c r="C53" s="4">
+      <c r="C53">
         <v>-9.8711824254379577E-2</v>
       </c>
-      <c r="D53" s="4">
+      <c r="D53">
         <v>-8.1075298149938829E-2</v>
       </c>
-      <c r="E53" s="4">
+      <c r="E53">
         <v>1</v>
       </c>
-      <c r="F53" s="4"/>
-      <c r="G53" s="4"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A54" s="4" t="s">
+      <c r="A54" t="s">
         <v>6</v>
       </c>
-      <c r="B54" s="4">
+      <c r="B54">
         <v>0.62623626351475892</v>
       </c>
-      <c r="C54" s="4">
+      <c r="C54">
         <v>0.91720765647857772</v>
       </c>
-      <c r="D54" s="4">
+      <c r="D54">
         <v>0.25911804999819832</v>
       </c>
-      <c r="E54" s="4">
+      <c r="E54">
         <v>-7.7632697598269476E-2</v>
       </c>
-      <c r="F54" s="4">
+      <c r="F54">
         <v>1</v>
       </c>
-      <c r="G54" s="4"/>
     </row>
     <row r="55" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="5" t="s">
+      <c r="A55" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B55" s="5">
+      <c r="B55" s="4">
         <v>-0.10708498611644857</v>
       </c>
-      <c r="C55" s="5">
+      <c r="C55" s="4">
         <v>-0.14856684900845371</v>
       </c>
-      <c r="D55" s="5">
+      <c r="D55" s="4">
         <v>-0.16079185436517709</v>
       </c>
-      <c r="E55" s="5">
+      <c r="E55" s="4">
         <v>2.176289371929899E-2</v>
       </c>
-      <c r="F55" s="5">
+      <c r="F55" s="4">
         <v>-0.17637769567516345</v>
       </c>
-      <c r="G55" s="5">
+      <c r="G55" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="82" spans="6:7" x14ac:dyDescent="0.3">
-      <c r="F82" s="9" t="s">
+      <c r="F82" s="7" t="s">
         <v>10</v>
       </c>
       <c r="G82" t="s">
@@ -24658,7 +26714,7 @@
       <c r="F83" t="s">
         <v>13</v>
       </c>
-      <c r="G83" s="11">
+      <c r="G83" s="14">
         <v>24</v>
       </c>
     </row>
@@ -24666,7 +26722,7 @@
       <c r="F84" t="s">
         <v>14</v>
       </c>
-      <c r="G84" s="11">
+      <c r="G84" s="14">
         <v>45</v>
       </c>
     </row>
@@ -24688,502 +26744,508 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:B61"/>
+  <dimension ref="A1:B63"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9" customWidth="1"/>
+    <col min="1" max="1" width="12.5546875" style="16" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="17" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="18">
         <v>87808</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="18">
         <v>96364</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="A4" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="18">
         <v>90582</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="A5" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="18">
         <v>95832</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="A6" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="18">
         <v>98707</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="A7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="18">
         <v>98061</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+      <c r="A8" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="18">
         <v>100255</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+      <c r="A9" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="18">
         <v>105651</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+      <c r="A10" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="18">
         <v>99405</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+      <c r="A11" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="18">
         <v>102381</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+      <c r="A12" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="18">
         <v>106716</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+      <c r="A13" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="18">
         <v>111524</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+      <c r="A14" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="18">
         <v>104985</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
+      <c r="A15" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="18">
         <v>106627</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+      <c r="A16" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="18">
         <v>106374</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
+      <c r="A17" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="B17">
+      <c r="B17" s="18">
         <v>105689</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
+      <c r="A18" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="B18">
+      <c r="B18" s="18">
         <v>107937</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
+      <c r="A19" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="B19">
+      <c r="B19" s="18">
         <v>113121</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
+      <c r="A20" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="B20">
+      <c r="B20" s="18">
         <v>117240</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
+      <c r="A21" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="B21">
+      <c r="B21" s="18">
         <v>117545</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
+      <c r="A22" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="B22">
+      <c r="B22" s="18">
         <v>114472</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
+      <c r="A23" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="B23">
+      <c r="B23" s="18">
         <v>114462</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
+      <c r="A24" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="B24">
+      <c r="B24" s="18">
         <v>121678</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
+      <c r="A25" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="B25">
+      <c r="B25" s="18">
         <v>124990</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
+      <c r="A26" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="B26">
+      <c r="B26" s="18">
         <v>115698</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
+      <c r="A27" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="B27">
+      <c r="B27" s="18">
         <v>118914</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
+      <c r="A28" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="B28">
+      <c r="B28" s="18">
         <v>119004</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
+      <c r="A29" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="B29">
+      <c r="B29" s="18">
         <v>123954</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
+      <c r="A30" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="B30">
+      <c r="B30" s="18">
         <v>126494</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
+      <c r="A31" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="B31">
+      <c r="B31" s="18">
         <v>131204</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
+      <c r="A32" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="B32">
+      <c r="B32" s="18">
         <v>132859</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
+      <c r="A33" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="B33">
+      <c r="B33" s="18">
         <v>133709</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
+      <c r="A34" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="B34">
+      <c r="B34" s="18">
         <v>130755</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
+      <c r="A35" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="B35">
+      <c r="B35" s="18">
         <v>129440</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
+      <c r="A36" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="B36">
+      <c r="B36" s="18">
         <v>135696</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
+      <c r="A37" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="B37">
+      <c r="B37" s="18">
         <v>136566</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
+      <c r="A38" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="B38">
+      <c r="B38" s="18">
         <v>136640</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
+      <c r="A39" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="B39">
+      <c r="B39" s="18">
         <v>133780</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
+      <c r="A40" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="B40">
+      <c r="B40" s="18">
         <v>134630</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
+      <c r="A41" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="B41">
+      <c r="B41" s="18">
         <v>135397</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
+      <c r="A42" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="B42">
+      <c r="B42" s="18">
         <v>138166</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
+      <c r="A43" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="B43">
+      <c r="B43" s="18">
         <v>144659</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
+      <c r="A44" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="B44">
+      <c r="B44" s="18">
         <v>144896</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
+      <c r="A45" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="B45">
+      <c r="B45" s="18">
         <v>148857</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
+      <c r="A46" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="B46">
+      <c r="B46" s="18">
         <v>144603</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
+      <c r="A47" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="B47">
+      <c r="B47" s="18">
         <v>144497</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
+      <c r="A48" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="B48">
+      <c r="B48" s="18">
         <v>146070</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
+      <c r="A49" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="B49">
+      <c r="B49" s="18">
         <v>154181</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
+      <c r="A50" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="B50">
+      <c r="B50" s="18">
         <v>144519</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
+      <c r="A51" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="B51">
+      <c r="B51" s="18">
         <v>151971</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
+      <c r="A52" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="B52">
+      <c r="B52" s="18">
         <v>150102</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
+      <c r="A53" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="B53">
+      <c r="B53" s="18">
         <v>150294</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
+      <c r="A54" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="B54">
+      <c r="B54" s="18">
         <v>153369</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
+      <c r="A55" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="B55">
+      <c r="B55" s="18">
         <v>157632</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
+      <c r="A56" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="B56">
+      <c r="B56" s="18">
         <v>158664</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
+      <c r="A57" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="B57">
+      <c r="B57" s="18">
         <v>157602</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
+      <c r="A58" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="B58">
+      <c r="B58" s="18">
         <v>158864</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
+      <c r="A59" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="B59">
+      <c r="B59" s="18">
         <v>160030</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
+      <c r="A60" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="B60">
+      <c r="B60" s="18">
         <v>163789</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A61" t="s">
+      <c r="A61" s="16" t="s">
         <v>78</v>
       </c>
-      <c r="B61">
+      <c r="B61" s="18">
         <v>171561</v>
       </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A63" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="B63" s="16"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
